--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.7685712217138</v>
+        <v>27.26820735524811</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.74696371697932</v>
+        <v>22.76337417231638</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.1596218970646</v>
+        <v>26.56535958619484</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.31147139337615</v>
+        <v>27.57654397840379</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26.38181340960843</v>
+        <v>27.83809992261721</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34.24012523158465</v>
+        <v>26.18276018308567</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.02723100052093</v>
+        <v>27.0380931977091</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27.35139170457453</v>
+        <v>22.62651900004813</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.22582649537623</v>
+        <v>26.10139853981979</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.62925357169811</v>
+        <v>27.58092828884762</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26.87368784271873</v>
+        <v>27.92230767681462</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33.69072829904816</v>
+        <v>25.76522336159171</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30.57721517710425</v>
+        <v>26.84704415262815</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.89199120500927</v>
+        <v>22.51362959460813</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>30.29102284544801</v>
+        <v>26.56574373682612</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.32134437333567</v>
+        <v>27.06329987679315</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26.42752953970465</v>
+        <v>28.40507283640475</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33.66697196730171</v>
+        <v>26.15519796346696</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.88594306835301</v>
+        <v>26.61761894019854</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>26.86835968363642</v>
+        <v>22.72877633434665</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30.32702942870674</v>
+        <v>26.54711248278866</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25.67385148261388</v>
+        <v>27.80581982866345</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.51190566045111</v>
+        <v>27.7921348386126</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.69194106459314</v>
+        <v>25.86638534306257</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.20175510583097</v>
+        <v>26.52435992921557</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.94005306334276</v>
+        <v>22.85855216129788</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30.05233628901915</v>
+        <v>26.66091243988392</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25.0177894147452</v>
+        <v>27.86838336552551</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26.21135270510835</v>
+        <v>27.91542652602702</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>33.37132131347587</v>
+        <v>26.4978122614127</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>31.25694684529882</v>
+        <v>27.36332310040317</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>26.91186091777035</v>
+        <v>23.0645942534083</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.96339314332569</v>
+        <v>26.64367591681433</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25.69592961666574</v>
+        <v>27.33811227871426</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>26.12577325024375</v>
+        <v>28.13684994318376</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>33.5641986858901</v>
+        <v>26.36500024450351</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>31.02317143651297</v>
+        <v>27.02455745292325</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.73302396972722</v>
+        <v>23.08072244800823</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30.57905068285054</v>
+        <v>26.49491574281396</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.36687220639953</v>
+        <v>27.53214050459923</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>26.65321915309869</v>
+        <v>27.57042508498531</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>33.28512115236494</v>
+        <v>26.16613699460336</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30.91439965925603</v>
+        <v>26.9070105482957</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>27.05103217446752</v>
+        <v>22.85655356521649</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30.28557195329985</v>
+        <v>26.46463952061982</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>24.83962396816479</v>
+        <v>27.82484746743413</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>26.27332137629466</v>
+        <v>28.10974637647266</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>33.03469983945652</v>
+        <v>26.2276601924936</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27.18900101479478</v>
+        <v>31.21561173060973</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>23.81155783282566</v>
+        <v>31.23256189157066</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18.85037405175945</v>
+        <v>20.4625227943984</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>31.26412399872858</v>
+        <v>27.07629045983198</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.81763407246782</v>
+        <v>32.78576674010782</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.76346347329229</v>
+        <v>32.39723087727887</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>27.43621792692548</v>
+        <v>31.66990152315744</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>24.40915602507034</v>
+        <v>31.29519065498627</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>19.37348317958294</v>
+        <v>20.28771808827805</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.95873752248382</v>
+        <v>27.09379325691478</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>29.7525379830646</v>
+        <v>33.31891194506991</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>24.85933990050036</v>
+        <v>32.29875196484136</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>27.56453879334844</v>
+        <v>31.95851974513182</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>24.31451636237619</v>
+        <v>31.48874161826241</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18.88822453226379</v>
+        <v>20.19744345315933</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>31.16002246539269</v>
+        <v>27.20258633861287</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>29.06729232795826</v>
+        <v>33.63988543574977</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>24.74759085411829</v>
+        <v>32.5714953158431</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>26.84207450779849</v>
+        <v>31.2149648006961</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>24.32343758036641</v>
+        <v>31.1897943812745</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>19.27316215620736</v>
+        <v>19.9599863964372</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>30.24412982985736</v>
+        <v>27.54678201679183</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>29.28123983859001</v>
+        <v>33.29458679646932</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>24.88685545909632</v>
+        <v>32.87934731244329</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>26.73112544765393</v>
+        <v>31.243085615119</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>24.55840266223543</v>
+        <v>31.45605383840599</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>19.20145356041262</v>
+        <v>19.73988137307045</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>31.3874262009207</v>
+        <v>26.55987839407202</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>29.10298788237693</v>
+        <v>32.75254425190735</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25.01015324799608</v>
+        <v>32.71191626877106</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>27.05054395307626</v>
+        <v>31.16985121171316</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>24.44688772244783</v>
+        <v>31.10805591976087</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>19.12656685641817</v>
+        <v>20.25088676418562</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>30.74590444124205</v>
+        <v>27.21803178515476</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29.15281425070338</v>
+        <v>33.6118259461348</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24.97439485537245</v>
+        <v>32.22564664429382</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>27.1010155506107</v>
+        <v>31.34331439274063</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>24.59448646331187</v>
+        <v>30.77275760189894</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>19.18411849762045</v>
+        <v>19.93931637235838</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>31.01495173452441</v>
+        <v>26.69173154095892</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>28.8023314951487</v>
+        <v>32.29234917702178</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>25.11826238240954</v>
+        <v>32.85725465573004</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>27.18669653301271</v>
+        <v>31.49774676018286</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>24.54859998289309</v>
+        <v>31.9195771536226</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>19.09476220272683</v>
+        <v>19.84499757488552</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>30.86831930223365</v>
+        <v>26.8738546788278</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>29.20561687364668</v>
+        <v>32.62811045859182</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>25.07361184723911</v>
+        <v>32.0180792118006</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>28.27969565262893</v>
+        <v>26.86257551862657</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>31.23913222613879</v>
+        <v>32.03973107703138</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>24.87012847910373</v>
+        <v>20.91613735647671</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>34.83442566955313</v>
+        <v>31.6341894955043</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>30.01664104671616</v>
+        <v>29.47757738776341</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>30.70935536472355</v>
+        <v>31.7713358442604</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>28.09751230028306</v>
+        <v>26.49044286069172</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.19155085437653</v>
+        <v>31.8980077798649</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>25.27918029021187</v>
+        <v>21.50757674528077</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>34.43664044928001</v>
+        <v>31.45630300100595</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>30.45764468199892</v>
+        <v>29.18583583848569</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>30.33142142333827</v>
+        <v>32.31109833023776</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>28.28021437185279</v>
+        <v>26.46932652272743</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>30.5846818156231</v>
+        <v>31.94291114370471</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>25.4641825977335</v>
+        <v>20.93257011854202</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>33.97323565004603</v>
+        <v>31.20614571674951</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>30.22366858963852</v>
+        <v>28.93415993726917</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>31.05745284769051</v>
+        <v>32.07001705044251</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>28.26206044697107</v>
+        <v>26.54483236139925</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>31.1901793015538</v>
+        <v>31.42693284881153</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>25.1515890777531</v>
+        <v>20.6161153050515</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>34.73929363874178</v>
+        <v>30.78042752475126</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>30.60021423912585</v>
+        <v>28.79414677999626</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30.48123899577994</v>
+        <v>31.72882448013796</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>28.48116596843047</v>
+        <v>26.88383887068428</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>31.44953731913791</v>
+        <v>32.33374182945461</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>25.15073247703</v>
+        <v>20.41612414624128</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>34.6443050034154</v>
+        <v>31.70845421759727</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>30.47584905332564</v>
+        <v>28.82627550275753</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>29.80278862225838</v>
+        <v>32.33472198235618</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>28.45673191167115</v>
+        <v>26.69878938622192</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>30.88604476745743</v>
+        <v>32.06188207975346</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>25.19050774242635</v>
+        <v>20.49291205465813</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>35.40701568832119</v>
+        <v>30.64946588465225</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>30.14632937656295</v>
+        <v>28.92064521620628</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>30.4964504552819</v>
+        <v>32.23201427504416</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>28.7827342360353</v>
+        <v>27.15105772372667</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>30.83196551599984</v>
+        <v>31.53124142842616</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>25.08093719616624</v>
+        <v>20.71413091756393</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>34.29781580098922</v>
+        <v>30.98137023090748</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>30.2438130242992</v>
+        <v>29.14970875613338</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>29.60272101508636</v>
+        <v>31.47532496709883</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>28.25194291190281</v>
+        <v>27.02886337840642</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>30.37910005971159</v>
+        <v>31.86696192915065</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>25.64033778440107</v>
+        <v>20.92479535574887</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>34.77711190562247</v>
+        <v>31.14271445822162</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>30.640227922222</v>
+        <v>29.21030810619571</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>30.31844019759974</v>
+        <v>32.45732248372147</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>31.38751521926305</v>
+        <v>27.69073485074594</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>28.30544733552558</v>
+        <v>27.17780855805283</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>23.56599636240206</v>
+        <v>25.2774744044636</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>28.96035799686905</v>
+        <v>23.56962117241441</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>31.76584605477537</v>
+        <v>24.46228909283809</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>23.45290374496381</v>
+        <v>27.78303317192934</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>32.30551777508295</v>
+        <v>28.00032824328191</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>27.9059167647811</v>
+        <v>27.62302337677495</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>23.7444800078453</v>
+        <v>25.16196598987318</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>29.29310751759079</v>
+        <v>23.78990049869288</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>31.81878432015928</v>
+        <v>24.63407224245279</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>23.7759643825864</v>
+        <v>28.38060728570726</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>31.37597190186827</v>
+        <v>27.69160413495035</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>27.47832093574231</v>
+        <v>27.13027763398771</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>23.57887059366534</v>
+        <v>25.29000324767474</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>29.07912532429788</v>
+        <v>23.3332849927205</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>31.67025692055432</v>
+        <v>24.90062953414963</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>24.05714783094242</v>
+        <v>28.08839864879271</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>31.29743634564299</v>
+        <v>27.75868904356634</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>27.51092304004051</v>
+        <v>26.96969470184613</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>23.96137253250837</v>
+        <v>25.44262728328425</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>29.34495245302899</v>
+        <v>23.88371380100283</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>31.81351536798653</v>
+        <v>24.95528737655811</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>23.72802373780413</v>
+        <v>27.65975184550659</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>31.66245599997129</v>
+        <v>27.47916143740281</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>28.85454314836661</v>
+        <v>26.75519854243664</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>23.73811670464028</v>
+        <v>25.53105045300199</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>28.55002014672084</v>
+        <v>23.90581466866033</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>31.34543878095911</v>
+        <v>24.64370418706067</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>23.91557075796833</v>
+        <v>27.80407042430097</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>30.83232701829946</v>
+        <v>27.5615840605401</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>27.9452074841854</v>
+        <v>27.75806195020364</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>23.80099406703476</v>
+        <v>25.78346926958536</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>29.37360202835402</v>
+        <v>23.86947855425171</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>31.94340451244934</v>
+        <v>24.79167902883627</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>23.97239953978401</v>
+        <v>27.98603506770539</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>30.6575158900391</v>
+        <v>27.40358660842023</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>28.1549024214176</v>
+        <v>26.84424487074593</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>23.87809611526907</v>
+        <v>25.33506641904499</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>29.00354242599375</v>
+        <v>23.47024941076233</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>30.98475203244057</v>
+        <v>24.56237571115285</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>23.58229922213293</v>
+        <v>27.96108117331191</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>30.96956939092486</v>
+        <v>27.6473124932569</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>27.3358015066372</v>
+        <v>26.96398221928373</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>23.71012194841506</v>
+        <v>25.60594699543593</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>28.69869305734189</v>
+        <v>23.65147212623387</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>32.35806281906829</v>
+        <v>24.76563956298045</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>23.72680252990835</v>
+        <v>27.78119347240415</v>
       </c>
     </row>
     <row r="194">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>29.86381196800826</v>
+        <v>32.08733532265042</v>
       </c>
     </row>
     <row r="195">
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>30.96771382749294</v>
+        <v>29.54236120706078</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>33.89217983814833</v>
+        <v>21.44905278256461</v>
       </c>
     </row>
     <row r="197">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>30.42168352629773</v>
+        <v>29.27850583420894</v>
       </c>
     </row>
     <row r="198">
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>35.26508269762374</v>
+        <v>27.00379555645868</v>
       </c>
     </row>
     <row r="199">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>23.44603156494141</v>
+        <v>27.75361570872836</v>
       </c>
     </row>
     <row r="200">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>29.41812559095553</v>
+        <v>32.12524938051641</v>
       </c>
     </row>
     <row r="201">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>31.38778327315257</v>
+        <v>29.97434752250016</v>
       </c>
     </row>
     <row r="202">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>34.7048869527034</v>
+        <v>21.48431277361255</v>
       </c>
     </row>
     <row r="203">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>30.50718551506303</v>
+        <v>29.53875567216305</v>
       </c>
     </row>
     <row r="204">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>35.75892861639846</v>
+        <v>27.01128204085863</v>
       </c>
     </row>
     <row r="205">
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>23.67250467050538</v>
+        <v>27.44371707198711</v>
       </c>
     </row>
     <row r="206">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>29.66299956441354</v>
+        <v>31.82389436284716</v>
       </c>
     </row>
     <row r="207">
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>31.43529655518313</v>
+        <v>30.14198796621121</v>
       </c>
     </row>
     <row r="208">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>33.96350892495541</v>
+        <v>20.81671352086336</v>
       </c>
     </row>
     <row r="209">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>30.44293322429853</v>
+        <v>29.10419441616307</v>
       </c>
     </row>
     <row r="210">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>35.99996567664733</v>
+        <v>26.97019730213788</v>
       </c>
     </row>
     <row r="211">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>23.81061831970065</v>
+        <v>27.36021100943511</v>
       </c>
     </row>
     <row r="212">
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>29.41150751262241</v>
+        <v>31.7362793159661</v>
       </c>
     </row>
     <row r="213">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>31.70294811517441</v>
+        <v>30.23769064786202</v>
       </c>
     </row>
     <row r="214">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>34.00649574673209</v>
+        <v>21.04656916909561</v>
       </c>
     </row>
     <row r="215">
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>30.40252811365268</v>
+        <v>29.46532481666899</v>
       </c>
     </row>
     <row r="216">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>35.41976023670306</v>
+        <v>26.58118761719163</v>
       </c>
     </row>
     <row r="217">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>23.50267142805393</v>
+        <v>27.2856848220486</v>
       </c>
     </row>
     <row r="218">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>29.87783877578271</v>
+        <v>32.16375481038816</v>
       </c>
     </row>
     <row r="219">
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>31.4904509018901</v>
+        <v>30.19664175424172</v>
       </c>
     </row>
     <row r="220">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>34.11889071578118</v>
+        <v>21.15623376389967</v>
       </c>
     </row>
     <row r="221">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>29.95239228161321</v>
+        <v>29.25472945779271</v>
       </c>
     </row>
     <row r="222">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>35.47822447431912</v>
+        <v>27.16349753160037</v>
       </c>
     </row>
     <row r="223">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>23.48862191903186</v>
+        <v>26.87321739047158</v>
       </c>
     </row>
     <row r="224">
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>29.23793145565302</v>
+        <v>31.9395538537552</v>
       </c>
     </row>
     <row r="225">
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>31.46819017531838</v>
+        <v>29.39050942847394</v>
       </c>
     </row>
     <row r="226">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>33.92656177537164</v>
+        <v>21.27712412391314</v>
       </c>
     </row>
     <row r="227">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>30.41654662457189</v>
+        <v>28.70120870858787</v>
       </c>
     </row>
     <row r="228">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>35.63151988934046</v>
+        <v>26.85954189776586</v>
       </c>
     </row>
     <row r="229">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>23.32040400191834</v>
+        <v>27.57854039162054</v>
       </c>
     </row>
     <row r="230">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>29.3648359258686</v>
+        <v>31.62378430914147</v>
       </c>
     </row>
     <row r="231">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>31.48571695155897</v>
+        <v>29.58969357142419</v>
       </c>
     </row>
     <row r="232">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>34.47632011373877</v>
+        <v>21.30041662968507</v>
       </c>
     </row>
     <row r="233">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>30.47025678894629</v>
+        <v>29.33734024624371</v>
       </c>
     </row>
     <row r="234">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>35.3527077201212</v>
+        <v>26.77785778172736</v>
       </c>
     </row>
     <row r="235">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>23.63938800477917</v>
+        <v>27.84930048794947</v>
       </c>
     </row>
     <row r="236">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>29.98580880978856</v>
+        <v>31.94651972838587</v>
       </c>
     </row>
     <row r="237">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>31.74978239039228</v>
+        <v>29.78808934898773</v>
       </c>
     </row>
     <row r="238">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>34.25935378113149</v>
+        <v>20.92109053352429</v>
       </c>
     </row>
     <row r="239">
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.61275716169565</v>
+        <v>28.59694532042602</v>
       </c>
     </row>
     <row r="240">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>36.10073392172784</v>
+        <v>26.78446635132097</v>
       </c>
     </row>
     <row r="241">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>23.79870164390296</v>
+        <v>27.31177617792365</v>
       </c>
     </row>
     <row r="242">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>31.2113552140237</v>
+        <v>32.08279055612566</v>
       </c>
     </row>
     <row r="243">
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>32.08712560235401</v>
+        <v>28.78452568938896</v>
       </c>
     </row>
     <row r="244">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>22.26088199373742</v>
+        <v>31.76303839276518</v>
       </c>
     </row>
     <row r="245">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>26.24013899988044</v>
+        <v>27.82298139574041</v>
       </c>
     </row>
     <row r="246">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>35.26903455548985</v>
+        <v>29.66590597500727</v>
       </c>
     </row>
     <row r="247">
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>22.21235959816568</v>
+        <v>26.48254424942154</v>
       </c>
     </row>
     <row r="248">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>30.86665355186806</v>
+        <v>31.99100728943408</v>
       </c>
     </row>
     <row r="249">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>32.01004512905312</v>
+        <v>29.04600544596466</v>
       </c>
     </row>
     <row r="250">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>22.08507559129722</v>
+        <v>32.22386680458384</v>
       </c>
     </row>
     <row r="251">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>26.49788249793045</v>
+        <v>27.14296479525022</v>
       </c>
     </row>
     <row r="252">
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>35.04294342552082</v>
+        <v>29.74575825569184</v>
       </c>
     </row>
     <row r="253">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>21.83390268224161</v>
+        <v>26.00106672863897</v>
       </c>
     </row>
     <row r="254">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>31.4993551528826</v>
+        <v>32.37559721062974</v>
       </c>
     </row>
     <row r="255">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>31.3163373812044</v>
+        <v>29.14873419783439</v>
       </c>
     </row>
     <row r="256">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>22.37189818988423</v>
+        <v>31.78753646382612</v>
       </c>
     </row>
     <row r="257">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>26.88223665067425</v>
+        <v>28.19464868618641</v>
       </c>
     </row>
     <row r="258">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>35.44121084689555</v>
+        <v>29.26175771675743</v>
       </c>
     </row>
     <row r="259">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>21.95113165660852</v>
+        <v>25.83209677005809</v>
       </c>
     </row>
     <row r="260">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>31.2472721864904</v>
+        <v>32.39583137029114</v>
       </c>
     </row>
     <row r="261">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>31.83985497903497</v>
+        <v>28.97954643998763</v>
       </c>
     </row>
     <row r="262">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>23.02933332344634</v>
+        <v>31.90330556382823</v>
       </c>
     </row>
     <row r="263">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>26.74795881755995</v>
+        <v>27.82331725736197</v>
       </c>
     </row>
     <row r="264">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>35.16397779418303</v>
+        <v>29.34016409991086</v>
       </c>
     </row>
     <row r="265">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>22.00699574263617</v>
+        <v>26.37725683018786</v>
       </c>
     </row>
     <row r="266">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>30.80447918945095</v>
+        <v>32.32732863266973</v>
       </c>
     </row>
     <row r="267">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>31.48569065206819</v>
+        <v>29.5490725324159</v>
       </c>
     </row>
     <row r="268">
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>22.81285619180772</v>
+        <v>31.60971304561649</v>
       </c>
     </row>
     <row r="269">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>26.64513493411329</v>
+        <v>27.39054087857551</v>
       </c>
     </row>
     <row r="270">
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>35.41275879274924</v>
+        <v>29.60854701444795</v>
       </c>
     </row>
     <row r="271">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>22.53323373544331</v>
+        <v>26.01864263216497</v>
       </c>
     </row>
     <row r="272">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>30.30349837014931</v>
+        <v>32.40735907062297</v>
       </c>
     </row>
     <row r="273">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>32.15386960766946</v>
+        <v>28.97967731131625</v>
       </c>
     </row>
     <row r="274">
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>22.51676668862845</v>
+        <v>31.69513591921296</v>
       </c>
     </row>
     <row r="275">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>26.75624608508246</v>
+        <v>28.25224455052596</v>
       </c>
     </row>
     <row r="276">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>34.92200274186739</v>
+        <v>29.71225713789203</v>
       </c>
     </row>
     <row r="277">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>22.02949863537357</v>
+        <v>26.53096412359495</v>
       </c>
     </row>
     <row r="278">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>31.18717409438522</v>
+        <v>32.45203979607459</v>
       </c>
     </row>
     <row r="279">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>32.50491326704456</v>
+        <v>28.82816819682402</v>
       </c>
     </row>
     <row r="280">
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>22.73008863927916</v>
+        <v>31.81024325144514</v>
       </c>
     </row>
     <row r="281">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>26.97748739258937</v>
+        <v>27.74091612701227</v>
       </c>
     </row>
     <row r="282">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>35.14610350677135</v>
+        <v>29.40845436337704</v>
       </c>
     </row>
     <row r="283">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>22.06388644369132</v>
+        <v>26.28755402719743</v>
       </c>
     </row>
     <row r="284">
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>30.79313213401688</v>
+        <v>32.15246783693067</v>
       </c>
     </row>
     <row r="285">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>31.59283819174354</v>
+        <v>29.10828924695525</v>
       </c>
     </row>
     <row r="286">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>22.04233568427229</v>
+        <v>31.56053271280701</v>
       </c>
     </row>
     <row r="287">
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>26.4472266528826</v>
+        <v>27.77403943989931</v>
       </c>
     </row>
     <row r="288">
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>35.01639312614102</v>
+        <v>28.75842213961868</v>
       </c>
     </row>
     <row r="289">
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>22.15819000774128</v>
+        <v>26.61951240118154</v>
       </c>
     </row>
     <row r="290">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>25.14380631028451</v>
+        <v>24.77702954475587</v>
       </c>
     </row>
     <row r="291">
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>32.39534156036687</v>
+        <v>26.58494702520998</v>
       </c>
     </row>
     <row r="292">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>30.66279935725104</v>
+        <v>24.8722578291718</v>
       </c>
     </row>
     <row r="293">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>29.04009752578525</v>
+        <v>27.35169025471847</v>
       </c>
     </row>
     <row r="294">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>29.27655254123958</v>
+        <v>31.44508440313093</v>
       </c>
     </row>
     <row r="295">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>24.15001337995582</v>
+        <v>20.28664506426645</v>
       </c>
     </row>
     <row r="296">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>24.86653352027805</v>
+        <v>25.09618414554059</v>
       </c>
     </row>
     <row r="297">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>32.4287870550054</v>
+        <v>26.9231424541343</v>
       </c>
     </row>
     <row r="298">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>30.94623116753882</v>
+        <v>25.16496005341232</v>
       </c>
     </row>
     <row r="299">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>29.48409269756917</v>
+        <v>27.86435333130686</v>
       </c>
     </row>
     <row r="300">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>30.08891553047687</v>
+        <v>30.74794600318095</v>
       </c>
     </row>
     <row r="301">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>24.25732135490079</v>
+        <v>20.33650147018315</v>
       </c>
     </row>
     <row r="302">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>24.979656089563</v>
+        <v>25.08766445476347</v>
       </c>
     </row>
     <row r="303">
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>32.03719597640973</v>
+        <v>26.84640598498187</v>
       </c>
     </row>
     <row r="304">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>30.20506620776887</v>
+        <v>25.23643990422977</v>
       </c>
     </row>
     <row r="305">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>29.49965652106242</v>
+        <v>26.95295669331309</v>
       </c>
     </row>
     <row r="306">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>29.81069400988519</v>
+        <v>30.08580112792467</v>
       </c>
     </row>
     <row r="307">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>23.9870214314811</v>
+        <v>20.29092500302508</v>
       </c>
     </row>
     <row r="308">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>24.90318494610765</v>
+        <v>25.40786964980928</v>
       </c>
     </row>
     <row r="309">
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>31.99850369333414</v>
+        <v>26.93082703132433</v>
       </c>
     </row>
     <row r="310">
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>30.68057105826379</v>
+        <v>24.8953813824469</v>
       </c>
     </row>
     <row r="311">
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>29.52174336656533</v>
+        <v>27.40948727454032</v>
       </c>
     </row>
     <row r="312">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>29.75894807713147</v>
+        <v>30.83903951735321</v>
       </c>
     </row>
     <row r="313">
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>23.74261956898806</v>
+        <v>20.33923919817749</v>
       </c>
     </row>
     <row r="314">
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>25.06321835554537</v>
+        <v>25.24181765956448</v>
       </c>
     </row>
     <row r="315">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>32.22793159492804</v>
+        <v>26.34542591226167</v>
       </c>
     </row>
     <row r="316">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>30.5983994432039</v>
+        <v>24.79918658421266</v>
       </c>
     </row>
     <row r="317">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>29.02665567371562</v>
+        <v>26.77692773215824</v>
       </c>
     </row>
     <row r="318">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>29.92780128114618</v>
+        <v>30.79311481762828</v>
       </c>
     </row>
     <row r="319">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>24.3058199425863</v>
+        <v>20.12653735962228</v>
       </c>
     </row>
     <row r="320">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>25.10448783392158</v>
+        <v>25.36594324700481</v>
       </c>
     </row>
     <row r="321">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>32.41154222250524</v>
+        <v>26.93741494209276</v>
       </c>
     </row>
     <row r="322">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>30.53555812689558</v>
+        <v>24.88819514629873</v>
       </c>
     </row>
     <row r="323">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>29.06780531712569</v>
+        <v>27.15271637357252</v>
       </c>
     </row>
     <row r="324">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>30.275012128626</v>
+        <v>31.12899660844251</v>
       </c>
     </row>
     <row r="325">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>24.42562048354097</v>
+        <v>19.90362996555415</v>
       </c>
     </row>
     <row r="326">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>25.31837503923807</v>
+        <v>24.88151295897142</v>
       </c>
     </row>
     <row r="327">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>32.67411471606904</v>
+        <v>27.2173900548522</v>
       </c>
     </row>
     <row r="328">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>30.82866985988296</v>
+        <v>24.66306623264392</v>
       </c>
     </row>
     <row r="329">
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>29.4811184285038</v>
+        <v>26.62103085004649</v>
       </c>
     </row>
     <row r="330">
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>29.39122997921757</v>
+        <v>31.25235780918158</v>
       </c>
     </row>
     <row r="331">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>24.33934290230395</v>
+        <v>20.44454523800446</v>
       </c>
     </row>
     <row r="332">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>25.06484097865542</v>
+        <v>25.28483925959621</v>
       </c>
     </row>
     <row r="333">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>32.81987712220651</v>
+        <v>26.89710552216126</v>
       </c>
     </row>
     <row r="334">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>30.95186112596547</v>
+        <v>25.18236396032823</v>
       </c>
     </row>
     <row r="335">
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>29.02578404210187</v>
+        <v>27.54720478718497</v>
       </c>
     </row>
     <row r="336">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>29.97419476255186</v>
+        <v>31.28168860546676</v>
       </c>
     </row>
     <row r="337">
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>24.33048381225722</v>
+        <v>20.36739334265722</v>
       </c>
     </row>
     <row r="338">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>29.95312269850188</v>
+        <v>25.70925062098112</v>
       </c>
     </row>
     <row r="339">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>32.09311550549424</v>
+        <v>31.04537599909696</v>
       </c>
     </row>
     <row r="340">
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>27.02736179452094</v>
+        <v>17.94114648715123</v>
       </c>
     </row>
     <row r="341">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>33.9897605194319</v>
+        <v>29.87507626416812</v>
       </c>
     </row>
     <row r="342">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>27.3833002672366</v>
+        <v>29.04836818107147</v>
       </c>
     </row>
     <row r="343">
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>25.73546091660047</v>
+        <v>26.53135022585028</v>
       </c>
     </row>
     <row r="344">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>29.64319963517504</v>
+        <v>25.8352987395026</v>
       </c>
     </row>
     <row r="345">
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>32.80405967256565</v>
+        <v>31.0662557218727</v>
       </c>
     </row>
     <row r="346">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>26.6472218453152</v>
+        <v>18.32935856087592</v>
       </c>
     </row>
     <row r="347">
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>33.7343896051077</v>
+        <v>29.46362519914022</v>
       </c>
     </row>
     <row r="348">
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>27.29208917521041</v>
+        <v>28.57461191095105</v>
       </c>
     </row>
     <row r="349">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>25.72314602458026</v>
+        <v>26.56042484895995</v>
       </c>
     </row>
     <row r="350">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>29.55375697873153</v>
+        <v>25.89053263547772</v>
       </c>
     </row>
     <row r="351">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>32.45752874567304</v>
+        <v>30.80860381826332</v>
       </c>
     </row>
     <row r="352">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>26.52508751764739</v>
+        <v>18.36247823730911</v>
       </c>
     </row>
     <row r="353">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>33.72409855554822</v>
+        <v>29.23756588870105</v>
       </c>
     </row>
     <row r="354">
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>27.86706895796364</v>
+        <v>28.80806242424442</v>
       </c>
     </row>
     <row r="355">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>26.04235590363723</v>
+        <v>26.24825354044698</v>
       </c>
     </row>
     <row r="356">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>29.59504407369239</v>
+        <v>25.00755681022564</v>
       </c>
     </row>
     <row r="357">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>32.55905927716826</v>
+        <v>31.28401714643574</v>
       </c>
     </row>
     <row r="358">
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>27.08319230350196</v>
+        <v>18.13942056815578</v>
       </c>
     </row>
     <row r="359">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>34.40625794112353</v>
+        <v>29.31053961350003</v>
       </c>
     </row>
     <row r="360">
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>27.27145259636958</v>
+        <v>28.73012638344805</v>
       </c>
     </row>
     <row r="361">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>26.17638495059647</v>
+        <v>26.74211133740918</v>
       </c>
     </row>
     <row r="362">
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>29.20983484847211</v>
+        <v>25.58318700817073</v>
       </c>
     </row>
     <row r="363">
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>32.08096784204793</v>
+        <v>31.10786637441846</v>
       </c>
     </row>
     <row r="364">
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>26.97453912885998</v>
+        <v>18.09932546634991</v>
       </c>
     </row>
     <row r="365">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>34.17978380576166</v>
+        <v>29.55274479880319</v>
       </c>
     </row>
     <row r="366">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>27.05720118471454</v>
+        <v>28.70739159525363</v>
       </c>
     </row>
     <row r="367">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>25.99049513818465</v>
+        <v>26.45815526763996</v>
       </c>
     </row>
     <row r="368">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>29.63163722131587</v>
+        <v>25.48432953205291</v>
       </c>
     </row>
     <row r="369">
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>32.33365976102941</v>
+        <v>30.85270623125793</v>
       </c>
     </row>
     <row r="370">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>27.20638365644306</v>
+        <v>18.10273162168489</v>
       </c>
     </row>
     <row r="371">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>34.37713810232278</v>
+        <v>29.53561506979057</v>
       </c>
     </row>
     <row r="372">
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>27.033915014775</v>
+        <v>28.56982167040205</v>
       </c>
     </row>
     <row r="373">
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>25.64917117073972</v>
+        <v>26.82842507941692</v>
       </c>
     </row>
     <row r="374">
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>29.6950494829371</v>
+        <v>25.99423225347372</v>
       </c>
     </row>
     <row r="375">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>32.41478740460094</v>
+        <v>31.16976283595466</v>
       </c>
     </row>
     <row r="376">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>26.75323314546592</v>
+        <v>18.18381121932124</v>
       </c>
     </row>
     <row r="377">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>34.42200666626424</v>
+        <v>29.51996854342711</v>
       </c>
     </row>
     <row r="378">
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>27.40103291786422</v>
+        <v>29.18747236785293</v>
       </c>
     </row>
     <row r="379">
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>26.02851549629704</v>
+        <v>27.08725932148264</v>
       </c>
     </row>
     <row r="380">
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>29.43999959695497</v>
+        <v>25.63566092691616</v>
       </c>
     </row>
     <row r="381">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>32.80193551349753</v>
+        <v>31.00726105732797</v>
       </c>
     </row>
     <row r="382">
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>26.17092492488296</v>
+        <v>18.23378389607457</v>
       </c>
     </row>
     <row r="383">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>34.35162767215125</v>
+        <v>29.76416482740661</v>
       </c>
     </row>
     <row r="384">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>27.56129883227261</v>
+        <v>28.73487945256259</v>
       </c>
     </row>
     <row r="385">
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>25.81115263870747</v>
+        <v>26.74993110787512</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -451,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.26820735524811</v>
+        <v>30.0853187380475</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.76337417231638</v>
+        <v>23.12369601522129</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.56535958619484</v>
+        <v>27.26532160975045</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.57654397840379</v>
+        <v>26.85861460724102</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.83809992261721</v>
+        <v>27.5733656442835</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.18276018308567</v>
+        <v>28.26613509053244</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27.0380931977091</v>
+        <v>29.89369070365238</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.62651900004813</v>
+        <v>22.87845444676072</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26.10139853981979</v>
+        <v>27.21995466117444</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.58092828884762</v>
+        <v>27.03054725563269</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27.92230767681462</v>
+        <v>28.49678574744939</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.76522336159171</v>
+        <v>28.43509237705367</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26.84704415262815</v>
+        <v>30.07374912477554</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22.51362959460813</v>
+        <v>23.04631774045898</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.56574373682612</v>
+        <v>26.74079508798118</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.06329987679315</v>
+        <v>26.91463161036991</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.40507283640475</v>
+        <v>27.98607992743867</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26.15519796346696</v>
+        <v>29.08474204068694</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.61761894019854</v>
+        <v>29.93879149633678</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.72877633434665</v>
+        <v>23.133034898786</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.54711248278866</v>
+        <v>27.25446368892001</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.80581982866345</v>
+        <v>26.60714080600722</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.7921348386126</v>
+        <v>28.28887278626872</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.86638534306257</v>
+        <v>28.59897775964668</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.52435992921557</v>
+        <v>30.23377488268549</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22.85855216129788</v>
+        <v>22.85375110243023</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.66091243988392</v>
+        <v>27.64638430427586</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>27.86838336552551</v>
+        <v>26.54436650136627</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27.91542652602702</v>
+        <v>28.13337343288733</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.4978122614127</v>
+        <v>29.00731013014455</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.36332310040317</v>
+        <v>29.69936687992453</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>23.0645942534083</v>
+        <v>22.93287955853662</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>26.64367591681433</v>
+        <v>27.29109635655066</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>27.33811227871426</v>
+        <v>26.78622505916637</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.13684994318376</v>
+        <v>27.53552531550904</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26.36500024450351</v>
+        <v>28.40499949542222</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.02455745292325</v>
+        <v>29.6778391801997</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>23.08072244800823</v>
+        <v>23.1727144963326</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>26.49491574281396</v>
+        <v>27.01325632417877</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27.53214050459923</v>
+        <v>27.33903938453419</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27.57042508498531</v>
+        <v>27.75016405294309</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.16613699460336</v>
+        <v>28.29411863393847</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>26.9070105482957</v>
+        <v>30.24051967523399</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22.85655356521649</v>
+        <v>22.77960732642177</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>26.46463952061982</v>
+        <v>27.32594199225768</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>27.82484746743413</v>
+        <v>27.27367557567923</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.10974637647266</v>
+        <v>27.51963325171168</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>26.2276601924936</v>
+        <v>28.43794683967966</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31.21561173060973</v>
+        <v>32.07303485763677</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>31.23256189157066</v>
+        <v>30.84688142834338</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20.4625227943984</v>
+        <v>22.44592923236874</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>27.07629045983198</v>
+        <v>26.77590993869613</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32.78576674010782</v>
+        <v>31.15555976851631</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>32.39723087727887</v>
+        <v>29.89314116689913</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31.66990152315744</v>
+        <v>32.07003102410232</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>31.29519065498627</v>
+        <v>30.71362376141913</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>20.28771808827805</v>
+        <v>22.57250208966166</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.09379325691478</v>
+        <v>27.1972255427317</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>33.31891194506991</v>
+        <v>31.08462456199494</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>32.29875196484136</v>
+        <v>29.59171622733891</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>31.95851974513182</v>
+        <v>32.58675798974242</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>31.48874161826241</v>
+        <v>30.75261314439343</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20.19744345315933</v>
+        <v>22.45630349820185</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>27.20258633861287</v>
+        <v>27.31235595200049</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>33.63988543574977</v>
+        <v>30.69169950130432</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>32.5714953158431</v>
+        <v>30.03921361819298</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>31.2149648006961</v>
+        <v>32.36053216632335</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>31.1897943812745</v>
+        <v>30.35639330082552</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>19.9599863964372</v>
+        <v>22.9459986499997</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>27.54678201679183</v>
+        <v>27.24621017196735</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>33.29458679646932</v>
+        <v>31.24857789629164</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>32.87934731244329</v>
+        <v>30.36995805017136</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>31.243085615119</v>
+        <v>31.91139920571509</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>31.45605383840599</v>
+        <v>30.37688390136735</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>19.73988137307045</v>
+        <v>22.52489125549262</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.55987839407202</v>
+        <v>26.9128417096471</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.75254425190735</v>
+        <v>30.96989355208163</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>32.71191626877106</v>
+        <v>29.90630506594851</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>31.16985121171316</v>
+        <v>32.07841172142162</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>31.10805591976087</v>
+        <v>30.86076514406685</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>20.25088676418562</v>
+        <v>22.73000660611551</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.21803178515476</v>
+        <v>27.52861026891005</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>33.6118259461348</v>
+        <v>30.91176311031762</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>32.22564664429382</v>
+        <v>30.61536224233168</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>31.34331439274063</v>
+        <v>32.19004896545693</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30.77275760189894</v>
+        <v>30.34522911157405</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>19.93931637235838</v>
+        <v>22.48366936818038</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>26.69173154095892</v>
+        <v>27.2651204035143</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.29234917702178</v>
+        <v>30.92453070714119</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>32.85725465573004</v>
+        <v>30.01743117264935</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>31.49774676018286</v>
+        <v>32.14128685154849</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>31.9195771536226</v>
+        <v>30.58529316266471</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>19.84499757488552</v>
+        <v>22.53460041367748</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26.8738546788278</v>
+        <v>26.72316359096767</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>32.62811045859182</v>
+        <v>30.85539838633474</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>32.0180792118006</v>
+        <v>30.05987245345765</v>
       </c>
     </row>
     <row r="98">
@@ -1987,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>26.86257551862657</v>
+        <v>27.66950683805296</v>
       </c>
     </row>
     <row r="99">
@@ -2003,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>32.03973107703138</v>
+        <v>27.13782391973364</v>
       </c>
     </row>
     <row r="100">
@@ -2019,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>20.91613735647671</v>
+        <v>21.7228483936089</v>
       </c>
     </row>
     <row r="101">
@@ -2035,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>31.6341894955043</v>
+        <v>24.74560458124206</v>
       </c>
     </row>
     <row r="102">
@@ -2051,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>29.47757738776341</v>
+        <v>32.1508755266154</v>
       </c>
     </row>
     <row r="103">
@@ -2067,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>31.7713358442604</v>
+        <v>31.33743567651315</v>
       </c>
     </row>
     <row r="104">
@@ -2083,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>26.49044286069172</v>
+        <v>27.62646636716737</v>
       </c>
     </row>
     <row r="105">
@@ -2099,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.8980077798649</v>
+        <v>27.1660648574326</v>
       </c>
     </row>
     <row r="106">
@@ -2115,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>21.50757674528077</v>
+        <v>21.76288084093663</v>
       </c>
     </row>
     <row r="107">
@@ -2131,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>31.45630300100595</v>
+        <v>24.78885832333376</v>
       </c>
     </row>
     <row r="108">
@@ -2147,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>29.18583583848569</v>
+        <v>32.78889305319687</v>
       </c>
     </row>
     <row r="109">
@@ -2163,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>32.31109833023776</v>
+        <v>31.61906377743652</v>
       </c>
     </row>
     <row r="110">
@@ -2179,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>26.46932652272743</v>
+        <v>27.23001475995352</v>
       </c>
     </row>
     <row r="111">
@@ -2195,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>31.94291114370471</v>
+        <v>27.22243909200669</v>
       </c>
     </row>
     <row r="112">
@@ -2211,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>20.93257011854202</v>
+        <v>21.79698051122132</v>
       </c>
     </row>
     <row r="113">
@@ -2227,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>31.20614571674951</v>
+        <v>24.77727288241</v>
       </c>
     </row>
     <row r="114">
@@ -2243,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>28.93415993726917</v>
+        <v>32.60464645942106</v>
       </c>
     </row>
     <row r="115">
@@ -2259,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>32.07001705044251</v>
+        <v>32.49483021700793</v>
       </c>
     </row>
     <row r="116">
@@ -2275,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>26.54483236139925</v>
+        <v>27.7680198336144</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>31.42693284881153</v>
+        <v>27.79221006186055</v>
       </c>
     </row>
     <row r="118">
@@ -2307,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>20.6161153050515</v>
+        <v>21.8921716847523</v>
       </c>
     </row>
     <row r="119">
@@ -2323,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30.78042752475126</v>
+        <v>24.8111934441087</v>
       </c>
     </row>
     <row r="120">
@@ -2339,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>28.79414677999626</v>
+        <v>32.33531176172219</v>
       </c>
     </row>
     <row r="121">
@@ -2355,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>31.72882448013796</v>
+        <v>31.52681254180862</v>
       </c>
     </row>
     <row r="122">
@@ -2371,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>26.88383887068428</v>
+        <v>27.39701461809451</v>
       </c>
     </row>
     <row r="123">
@@ -2387,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>32.33374182945461</v>
+        <v>27.41507674545921</v>
       </c>
     </row>
     <row r="124">
@@ -2403,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>20.41612414624128</v>
+        <v>21.58004109099569</v>
       </c>
     </row>
     <row r="125">
@@ -2419,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>31.70845421759727</v>
+        <v>24.67080393674179</v>
       </c>
     </row>
     <row r="126">
@@ -2435,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>28.82627550275753</v>
+        <v>33.1883966328481</v>
       </c>
     </row>
     <row r="127">
@@ -2451,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>32.33472198235618</v>
+        <v>30.70508122922451</v>
       </c>
     </row>
     <row r="128">
@@ -2467,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>26.69878938622192</v>
+        <v>27.79987385755037</v>
       </c>
     </row>
     <row r="129">
@@ -2483,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>32.06188207975346</v>
+        <v>27.03697804640046</v>
       </c>
     </row>
     <row r="130">
@@ -2499,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>20.49291205465813</v>
+        <v>21.5829537906816</v>
       </c>
     </row>
     <row r="131">
@@ -2515,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>30.64946588465225</v>
+        <v>24.91905454203809</v>
       </c>
     </row>
     <row r="132">
@@ -2531,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>28.92064521620628</v>
+        <v>32.45842834817261</v>
       </c>
     </row>
     <row r="133">
@@ -2547,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>32.23201427504416</v>
+        <v>30.95211692543657</v>
       </c>
     </row>
     <row r="134">
@@ -2563,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.15105772372667</v>
+        <v>27.41289653274493</v>
       </c>
     </row>
     <row r="135">
@@ -2579,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>31.53124142842616</v>
+        <v>27.66690937920993</v>
       </c>
     </row>
     <row r="136">
@@ -2595,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>20.71413091756393</v>
+        <v>21.52691145292214</v>
       </c>
     </row>
     <row r="137">
@@ -2611,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>30.98137023090748</v>
+        <v>24.70397984009355</v>
       </c>
     </row>
     <row r="138">
@@ -2627,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>29.14970875613338</v>
+        <v>32.45235986805462</v>
       </c>
     </row>
     <row r="139">
@@ -2643,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>31.47532496709883</v>
+        <v>31.0854546885606</v>
       </c>
     </row>
     <row r="140">
@@ -2659,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>27.02886337840642</v>
+        <v>28.20234613567843</v>
       </c>
     </row>
     <row r="141">
@@ -2675,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>31.86696192915065</v>
+        <v>27.65435679439516</v>
       </c>
     </row>
     <row r="142">
@@ -2691,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>20.92479535574887</v>
+        <v>21.24613548561328</v>
       </c>
     </row>
     <row r="143">
@@ -2707,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>31.14271445822162</v>
+        <v>24.69658359988992</v>
       </c>
     </row>
     <row r="144">
@@ -2723,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>29.21030810619571</v>
+        <v>32.22290997000602</v>
       </c>
     </row>
     <row r="145">
@@ -2739,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>32.45732248372147</v>
+        <v>31.55605684267644</v>
       </c>
     </row>
     <row r="146">
@@ -2755,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>27.69073485074594</v>
+        <v>28.5629946491987</v>
       </c>
     </row>
     <row r="147">
@@ -2771,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>27.17780855805283</v>
+        <v>30.77454194026616</v>
       </c>
     </row>
     <row r="148">
@@ -2787,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>25.2774744044636</v>
+        <v>27.54879943231923</v>
       </c>
     </row>
     <row r="149">
@@ -2803,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>23.56962117241441</v>
+        <v>26.42043769967777</v>
       </c>
     </row>
     <row r="150">
@@ -2819,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>24.46228909283809</v>
+        <v>30.71108443900398</v>
       </c>
     </row>
     <row r="151">
@@ -2835,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>27.78303317192934</v>
+        <v>31.89130775774083</v>
       </c>
     </row>
     <row r="152">
@@ -2851,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>28.00032824328191</v>
+        <v>28.65442833239878</v>
       </c>
     </row>
     <row r="153">
@@ -2867,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>27.62302337677495</v>
+        <v>30.60860208239184</v>
       </c>
     </row>
     <row r="154">
@@ -2883,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>25.16196598987318</v>
+        <v>27.89429822245935</v>
       </c>
     </row>
     <row r="155">
@@ -2899,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>23.78990049869288</v>
+        <v>26.29974423851887</v>
       </c>
     </row>
     <row r="156">
@@ -2915,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>24.63407224245279</v>
+        <v>30.69225129262015</v>
       </c>
     </row>
     <row r="157">
@@ -2931,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>28.38060728570726</v>
+        <v>32.2920432197155</v>
       </c>
     </row>
     <row r="158">
@@ -2947,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>27.69160413495035</v>
+        <v>29.40216425950368</v>
       </c>
     </row>
     <row r="159">
@@ -2963,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>27.13027763398771</v>
+        <v>31.12799354698901</v>
       </c>
     </row>
     <row r="160">
@@ -2979,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>25.29000324767474</v>
+        <v>26.99391540885022</v>
       </c>
     </row>
     <row r="161">
@@ -2995,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>23.3332849927205</v>
+        <v>26.06682603775835</v>
       </c>
     </row>
     <row r="162">
@@ -3011,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>24.90062953414963</v>
+        <v>31.4779958449378</v>
       </c>
     </row>
     <row r="163">
@@ -3027,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>28.08839864879271</v>
+        <v>31.77190010906777</v>
       </c>
     </row>
     <row r="164">
@@ -3043,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>27.75868904356634</v>
+        <v>28.918951456341</v>
       </c>
     </row>
     <row r="165">
@@ -3059,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>26.96969470184613</v>
+        <v>31.04855603023831</v>
       </c>
     </row>
     <row r="166">
@@ -3075,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>25.44262728328425</v>
+        <v>27.15630532847723</v>
       </c>
     </row>
     <row r="167">
@@ -3091,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>23.88371380100283</v>
+        <v>26.17807281493502</v>
       </c>
     </row>
     <row r="168">
@@ -3107,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>24.95528737655811</v>
+        <v>30.07666522131515</v>
       </c>
     </row>
     <row r="169">
@@ -3123,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>27.65975184550659</v>
+        <v>31.67055554209665</v>
       </c>
     </row>
     <row r="170">
@@ -3139,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>27.47916143740281</v>
+        <v>28.7184533199484</v>
       </c>
     </row>
     <row r="171">
@@ -3155,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>26.75519854243664</v>
+        <v>30.42545146191644</v>
       </c>
     </row>
     <row r="172">
@@ -3171,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>25.53105045300199</v>
+        <v>27.85783064738067</v>
       </c>
     </row>
     <row r="173">
@@ -3187,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>23.90581466866033</v>
+        <v>25.81905825001109</v>
       </c>
     </row>
     <row r="174">
@@ -3203,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>24.64370418706067</v>
+        <v>30.94740256620453</v>
       </c>
     </row>
     <row r="175">
@@ -3219,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>27.80407042430097</v>
+        <v>32.04017742706655</v>
       </c>
     </row>
     <row r="176">
@@ -3235,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>27.5615840605401</v>
+        <v>29.2061300995677</v>
       </c>
     </row>
     <row r="177">
@@ -3251,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>27.75806195020364</v>
+        <v>30.36750453441212</v>
       </c>
     </row>
     <row r="178">
@@ -3267,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>25.78346926958536</v>
+        <v>27.72920810796261</v>
       </c>
     </row>
     <row r="179">
@@ -3283,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>23.86947855425171</v>
+        <v>26.19634510079635</v>
       </c>
     </row>
     <row r="180">
@@ -3299,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>24.79167902883627</v>
+        <v>30.77909283381314</v>
       </c>
     </row>
     <row r="181">
@@ -3315,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>27.98603506770539</v>
+        <v>32.14620806212114</v>
       </c>
     </row>
     <row r="182">
@@ -3331,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>27.40358660842023</v>
+        <v>28.84848226405982</v>
       </c>
     </row>
     <row r="183">
@@ -3347,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>26.84424487074593</v>
+        <v>30.62496594179443</v>
       </c>
     </row>
     <row r="184">
@@ -3363,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>25.33506641904499</v>
+        <v>27.42951351477685</v>
       </c>
     </row>
     <row r="185">
@@ -3379,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>23.47024941076233</v>
+        <v>26.09273693554986</v>
       </c>
     </row>
     <row r="186">
@@ -3395,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>24.56237571115285</v>
+        <v>31.1194727601923</v>
       </c>
     </row>
     <row r="187">
@@ -3411,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>27.96108117331191</v>
+        <v>32.21021345097125</v>
       </c>
     </row>
     <row r="188">
@@ -3427,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>27.6473124932569</v>
+        <v>29.24780345545017</v>
       </c>
     </row>
     <row r="189">
@@ -3443,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>26.96398221928373</v>
+        <v>30.42852249433754</v>
       </c>
     </row>
     <row r="190">
@@ -3459,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>25.60594699543593</v>
+        <v>27.99505306182169</v>
       </c>
     </row>
     <row r="191">
@@ -3475,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>23.65147212623387</v>
+        <v>25.68234135450083</v>
       </c>
     </row>
     <row r="192">
@@ -3491,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>24.76563956298045</v>
+        <v>31.03700565402474</v>
       </c>
     </row>
     <row r="193">
@@ -3507,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>27.78119347240415</v>
+        <v>32.18659436457719</v>
       </c>
     </row>
     <row r="194">
@@ -3523,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>32.08733532265042</v>
+        <v>28.97730019028065</v>
       </c>
     </row>
     <row r="195">
@@ -3539,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>29.54236120706078</v>
+        <v>32.17936589084081</v>
       </c>
     </row>
     <row r="196">
@@ -3555,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>21.44905278256461</v>
+        <v>15.7501461715677</v>
       </c>
     </row>
     <row r="197">
@@ -3571,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>29.27850583420894</v>
+        <v>30.1519411868662</v>
       </c>
     </row>
     <row r="198">
@@ -3587,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>27.00379555645868</v>
+        <v>30.0827927034048</v>
       </c>
     </row>
     <row r="199">
@@ -3603,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>27.75361570872836</v>
+        <v>25.04486042480135</v>
       </c>
     </row>
     <row r="200">
@@ -3619,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>32.12524938051641</v>
+        <v>28.99926805443888</v>
       </c>
     </row>
     <row r="201">
@@ -3635,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>29.97434752250016</v>
+        <v>32.15663116474247</v>
       </c>
     </row>
     <row r="202">
@@ -3651,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>21.48431277361255</v>
+        <v>15.92497788925971</v>
       </c>
     </row>
     <row r="203">
@@ -3667,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>29.53875567216305</v>
+        <v>30.39444284497853</v>
       </c>
     </row>
     <row r="204">
@@ -3683,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>27.01128204085863</v>
+        <v>30.507122558296</v>
       </c>
     </row>
     <row r="205">
@@ -3699,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>27.44371707198711</v>
+        <v>24.99023254966304</v>
       </c>
     </row>
     <row r="206">
@@ -3715,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>31.82389436284716</v>
+        <v>28.65655722203655</v>
       </c>
     </row>
     <row r="207">
@@ -3731,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>30.14198796621121</v>
+        <v>32.19961000112582</v>
       </c>
     </row>
     <row r="208">
@@ -3747,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>20.81671352086336</v>
+        <v>15.90093939961181</v>
       </c>
     </row>
     <row r="209">
@@ -3763,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>29.10419441616307</v>
+        <v>30.48627730236517</v>
       </c>
     </row>
     <row r="210">
@@ -3779,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>26.97019730213788</v>
+        <v>30.25481614385098</v>
       </c>
     </row>
     <row r="211">
@@ -3795,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>27.36021100943511</v>
+        <v>24.86300826459261</v>
       </c>
     </row>
     <row r="212">
@@ -3811,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>31.7362793159661</v>
+        <v>29.26529986985653</v>
       </c>
     </row>
     <row r="213">
@@ -3827,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>30.23769064786202</v>
+        <v>32.1894454916311</v>
       </c>
     </row>
     <row r="214">
@@ -3843,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>21.04656916909561</v>
+        <v>15.86934244140877</v>
       </c>
     </row>
     <row r="215">
@@ -3859,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>29.46532481666899</v>
+        <v>30.24005995544189</v>
       </c>
     </row>
     <row r="216">
@@ -3875,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>26.58118761719163</v>
+        <v>30.1952683884298</v>
       </c>
     </row>
     <row r="217">
@@ -3891,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>27.2856848220486</v>
+        <v>25.10674016284441</v>
       </c>
     </row>
     <row r="218">
@@ -3907,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>32.16375481038816</v>
+        <v>29.13461765723405</v>
       </c>
     </row>
     <row r="219">
@@ -3923,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>30.19664175424172</v>
+        <v>32.64442480970493</v>
       </c>
     </row>
     <row r="220">
@@ -3939,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>21.15623376389967</v>
+        <v>15.98903773708224</v>
       </c>
     </row>
     <row r="221">
@@ -3955,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>29.25472945779271</v>
+        <v>30.30769145498891</v>
       </c>
     </row>
     <row r="222">
@@ -3971,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>27.16349753160037</v>
+        <v>30.46750795630783</v>
       </c>
     </row>
     <row r="223">
@@ -3987,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>26.87321739047158</v>
+        <v>24.75682008606106</v>
       </c>
     </row>
     <row r="224">
@@ -4003,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>31.9395538537552</v>
+        <v>28.98977593450654</v>
       </c>
     </row>
     <row r="225">
@@ -4019,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>29.39050942847394</v>
+        <v>32.33886061093406</v>
       </c>
     </row>
     <row r="226">
@@ -4035,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>21.27712412391314</v>
+        <v>15.79830296147626</v>
       </c>
     </row>
     <row r="227">
@@ -4051,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>28.70120870858787</v>
+        <v>30.48166748876465</v>
       </c>
     </row>
     <row r="228">
@@ -4067,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>26.85954189776586</v>
+        <v>30.01353828839505</v>
       </c>
     </row>
     <row r="229">
@@ -4083,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>27.57854039162054</v>
+        <v>25.35349209701874</v>
       </c>
     </row>
     <row r="230">
@@ -4099,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>31.62378430914147</v>
+        <v>28.60540465286982</v>
       </c>
     </row>
     <row r="231">
@@ -4115,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>29.58969357142419</v>
+        <v>31.98783579441977</v>
       </c>
     </row>
     <row r="232">
@@ -4131,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>21.30041662968507</v>
+        <v>15.96577866481706</v>
       </c>
     </row>
     <row r="233">
@@ -4147,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>29.33734024624371</v>
+        <v>30.54121131398233</v>
       </c>
     </row>
     <row r="234">
@@ -4163,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>26.77785778172736</v>
+        <v>30.45000698383927</v>
       </c>
     </row>
     <row r="235">
@@ -4179,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>27.84930048794947</v>
+        <v>24.98991384848164</v>
       </c>
     </row>
     <row r="236">
@@ -4195,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>31.94651972838587</v>
+        <v>28.89256564630306</v>
       </c>
     </row>
     <row r="237">
@@ -4211,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>29.78808934898773</v>
+        <v>32.09046227818327</v>
       </c>
     </row>
     <row r="238">
@@ -4227,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>20.92109053352429</v>
+        <v>15.79495832299273</v>
       </c>
     </row>
     <row r="239">
@@ -4243,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>28.59694532042602</v>
+        <v>30.09613802764359</v>
       </c>
     </row>
     <row r="240">
@@ -4259,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>26.78446635132097</v>
+        <v>30.55622356415909</v>
       </c>
     </row>
     <row r="241">
@@ -4275,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>27.31177617792365</v>
+        <v>24.79735129227493</v>
       </c>
     </row>
     <row r="242">
@@ -4291,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>32.08279055612566</v>
+        <v>29.02451536523277</v>
       </c>
     </row>
     <row r="243">
@@ -4307,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>28.78452568938896</v>
+        <v>22.36270474569161</v>
       </c>
     </row>
     <row r="244">
@@ -4323,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>31.76303839276518</v>
+        <v>25.24710414769315</v>
       </c>
     </row>
     <row r="245">
@@ -4339,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>27.82298139574041</v>
+        <v>28.83643555795685</v>
       </c>
     </row>
     <row r="246">
@@ -4355,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>29.66590597500727</v>
+        <v>34.15056137677244</v>
       </c>
     </row>
     <row r="247">
@@ -4371,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>26.48254424942154</v>
+        <v>24.03717928657334</v>
       </c>
     </row>
     <row r="248">
@@ -4387,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>31.99100728943408</v>
+        <v>29.3377984289354</v>
       </c>
     </row>
     <row r="249">
@@ -4403,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>29.04600544596466</v>
+        <v>22.32107531592501</v>
       </c>
     </row>
     <row r="250">
@@ -4419,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>32.22386680458384</v>
+        <v>25.02484515905266</v>
       </c>
     </row>
     <row r="251">
@@ -4435,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>27.14296479525022</v>
+        <v>29.0672094852888</v>
       </c>
     </row>
     <row r="252">
@@ -4451,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>29.74575825569184</v>
+        <v>33.93505337503788</v>
       </c>
     </row>
     <row r="253">
@@ -4467,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>26.00106672863897</v>
+        <v>23.64125398313965</v>
       </c>
     </row>
     <row r="254">
@@ -4483,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>32.37559721062974</v>
+        <v>29.0558456028002</v>
       </c>
     </row>
     <row r="255">
@@ -4499,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>29.14873419783439</v>
+        <v>22.38692058250046</v>
       </c>
     </row>
     <row r="256">
@@ -4515,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>31.78753646382612</v>
+        <v>25.22145199606594</v>
       </c>
     </row>
     <row r="257">
@@ -4531,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>28.19464868618641</v>
+        <v>29.42776725204962</v>
       </c>
     </row>
     <row r="258">
@@ -4547,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>29.26175771675743</v>
+        <v>34.72900592267152</v>
       </c>
     </row>
     <row r="259">
@@ -4563,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>25.83209677005809</v>
+        <v>23.94039489463883</v>
       </c>
     </row>
     <row r="260">
@@ -4579,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>32.39583137029114</v>
+        <v>29.26054094834307</v>
       </c>
     </row>
     <row r="261">
@@ -4595,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>28.97954643998763</v>
+        <v>22.20989151065052</v>
       </c>
     </row>
     <row r="262">
@@ -4611,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>31.90330556382823</v>
+        <v>25.13862482788148</v>
       </c>
     </row>
     <row r="263">
@@ -4627,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>27.82331725736197</v>
+        <v>28.91620443972791</v>
       </c>
     </row>
     <row r="264">
@@ -4643,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>29.34016409991086</v>
+        <v>34.54480601747952</v>
       </c>
     </row>
     <row r="265">
@@ -4659,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>26.37725683018786</v>
+        <v>23.78038654071459</v>
       </c>
     </row>
     <row r="266">
@@ -4675,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>32.32732863266973</v>
+        <v>29.41809875462659</v>
       </c>
     </row>
     <row r="267">
@@ -4691,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>29.5490725324159</v>
+        <v>22.7786740566631</v>
       </c>
     </row>
     <row r="268">
@@ -4707,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>31.60971304561649</v>
+        <v>25.11593376917311</v>
       </c>
     </row>
     <row r="269">
@@ -4723,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>27.39054087857551</v>
+        <v>29.11641125899098</v>
       </c>
     </row>
     <row r="270">
@@ -4739,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>29.60854701444795</v>
+        <v>34.6713241225988</v>
       </c>
     </row>
     <row r="271">
@@ -4755,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>26.01864263216497</v>
+        <v>23.88253851028252</v>
       </c>
     </row>
     <row r="272">
@@ -4771,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>32.40735907062297</v>
+        <v>29.33168939578223</v>
       </c>
     </row>
     <row r="273">
@@ -4787,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>28.97967731131625</v>
+        <v>22.43763211993449</v>
       </c>
     </row>
     <row r="274">
@@ -4803,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>31.69513591921296</v>
+        <v>25.16783861203077</v>
       </c>
     </row>
     <row r="275">
@@ -4819,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>28.25224455052596</v>
+        <v>28.7757430184253</v>
       </c>
     </row>
     <row r="276">
@@ -4835,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>29.71225713789203</v>
+        <v>34.44212188971942</v>
       </c>
     </row>
     <row r="277">
@@ -4851,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>26.53096412359495</v>
+        <v>24.09815989481555</v>
       </c>
     </row>
     <row r="278">
@@ -4867,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>32.45203979607459</v>
+        <v>29.69079948207868</v>
       </c>
     </row>
     <row r="279">
@@ -4883,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>28.82816819682402</v>
+        <v>22.65001759793227</v>
       </c>
     </row>
     <row r="280">
@@ -4899,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>31.81024325144514</v>
+        <v>25.68466032383</v>
       </c>
     </row>
     <row r="281">
@@ -4915,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>27.74091612701227</v>
+        <v>28.7773850577043</v>
       </c>
     </row>
     <row r="282">
@@ -4931,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>29.40845436337704</v>
+        <v>34.73405424946419</v>
       </c>
     </row>
     <row r="283">
@@ -4947,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>26.28755402719743</v>
+        <v>24.02270926287277</v>
       </c>
     </row>
     <row r="284">
@@ -4963,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>32.15246783693067</v>
+        <v>29.90697630509682</v>
       </c>
     </row>
     <row r="285">
@@ -4979,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>29.10828924695525</v>
+        <v>22.25346687849758</v>
       </c>
     </row>
     <row r="286">
@@ -4995,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>31.56053271280701</v>
+        <v>24.93214602647758</v>
       </c>
     </row>
     <row r="287">
@@ -5011,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>27.77403943989931</v>
+        <v>28.82609184133769</v>
       </c>
     </row>
     <row r="288">
@@ -5027,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>28.75842213961868</v>
+        <v>33.70234663165332</v>
       </c>
     </row>
     <row r="289">
@@ -5043,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>26.61951240118154</v>
+        <v>23.85267668671973</v>
       </c>
     </row>
     <row r="290">
@@ -5059,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>24.77702954475587</v>
+        <v>26.45301894287697</v>
       </c>
     </row>
     <row r="291">
@@ -5075,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>26.58494702520998</v>
+        <v>26.63507762620971</v>
       </c>
     </row>
     <row r="292">
@@ -5091,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>24.8722578291718</v>
+        <v>29.67112573435474</v>
       </c>
     </row>
     <row r="293">
@@ -5107,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>27.35169025471847</v>
+        <v>29.46310115289606</v>
       </c>
     </row>
     <row r="294">
@@ -5123,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>31.44508440313093</v>
+        <v>28.68074163836922</v>
       </c>
     </row>
     <row r="295">
@@ -5139,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>20.28664506426645</v>
+        <v>27.84019991018853</v>
       </c>
     </row>
     <row r="296">
@@ -5155,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>25.09618414554059</v>
+        <v>26.41589280984012</v>
       </c>
     </row>
     <row r="297">
@@ -5171,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>26.9231424541343</v>
+        <v>26.72590657652815</v>
       </c>
     </row>
     <row r="298">
@@ -5187,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>25.16496005341232</v>
+        <v>29.1796743985436</v>
       </c>
     </row>
     <row r="299">
@@ -5203,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>27.86435333130686</v>
+        <v>29.45017019633031</v>
       </c>
     </row>
     <row r="300">
@@ -5219,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>30.74794600318095</v>
+        <v>28.74580681175474</v>
       </c>
     </row>
     <row r="301">
@@ -5235,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>20.33650147018315</v>
+        <v>27.8703656288721</v>
       </c>
     </row>
     <row r="302">
@@ -5251,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>25.08766445476347</v>
+        <v>26.1987262290957</v>
       </c>
     </row>
     <row r="303">
@@ -5267,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>26.84640598498187</v>
+        <v>26.95514372273376</v>
       </c>
     </row>
     <row r="304">
@@ -5283,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>25.23643990422977</v>
+        <v>29.5361987486131</v>
       </c>
     </row>
     <row r="305">
@@ -5299,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>26.95295669331309</v>
+        <v>29.27848581201093</v>
       </c>
     </row>
     <row r="306">
@@ -5315,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>30.08580112792467</v>
+        <v>27.95773102070302</v>
       </c>
     </row>
     <row r="307">
@@ -5331,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>20.29092500302508</v>
+        <v>27.83390753567346</v>
       </c>
     </row>
     <row r="308">
@@ -5347,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>25.40786964980928</v>
+        <v>26.65676627909538</v>
       </c>
     </row>
     <row r="309">
@@ -5363,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>26.93082703132433</v>
+        <v>26.60757480459009</v>
       </c>
     </row>
     <row r="310">
@@ -5379,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>24.8953813824469</v>
+        <v>29.43698359191132</v>
       </c>
     </row>
     <row r="311">
@@ -5395,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>27.40948727454032</v>
+        <v>29.10063444108391</v>
       </c>
     </row>
     <row r="312">
@@ -5411,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>30.83903951735321</v>
+        <v>28.10740074437057</v>
       </c>
     </row>
     <row r="313">
@@ -5427,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>20.33923919817749</v>
+        <v>27.96187425167716</v>
       </c>
     </row>
     <row r="314">
@@ -5443,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>25.24181765956448</v>
+        <v>26.68743379559405</v>
       </c>
     </row>
     <row r="315">
@@ -5459,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>26.34542591226167</v>
+        <v>26.73189569886224</v>
       </c>
     </row>
     <row r="316">
@@ -5475,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>24.79918658421266</v>
+        <v>29.78049326423044</v>
       </c>
     </row>
     <row r="317">
@@ -5491,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>26.77692773215824</v>
+        <v>28.59525095593398</v>
       </c>
     </row>
     <row r="318">
@@ -5507,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>30.79311481762828</v>
+        <v>27.97486651654892</v>
       </c>
     </row>
     <row r="319">
@@ -5523,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>20.12653735962228</v>
+        <v>28.35951476904194</v>
       </c>
     </row>
     <row r="320">
@@ -5539,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>25.36594324700481</v>
+        <v>26.74394807625156</v>
       </c>
     </row>
     <row r="321">
@@ -5555,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>26.93741494209276</v>
+        <v>26.39601968269633</v>
       </c>
     </row>
     <row r="322">
@@ -5571,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>24.88819514629873</v>
+        <v>30.02874495700152</v>
       </c>
     </row>
     <row r="323">
@@ -5587,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>27.15271637357252</v>
+        <v>28.95395679325184</v>
       </c>
     </row>
     <row r="324">
@@ -5603,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>31.12899660844251</v>
+        <v>28.74576620242208</v>
       </c>
     </row>
     <row r="325">
@@ -5619,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>19.90362996555415</v>
+        <v>28.02064934077672</v>
       </c>
     </row>
     <row r="326">
@@ -5635,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>24.88151295897142</v>
+        <v>27.2046685059067</v>
       </c>
     </row>
     <row r="327">
@@ -5651,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>27.2173900548522</v>
+        <v>27.06191458416295</v>
       </c>
     </row>
     <row r="328">
@@ -5667,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>24.66306623264392</v>
+        <v>29.4964493903923</v>
       </c>
     </row>
     <row r="329">
@@ -5683,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>26.62103085004649</v>
+        <v>29.20148631410503</v>
       </c>
     </row>
     <row r="330">
@@ -5699,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>31.25235780918158</v>
+        <v>28.59407533873767</v>
       </c>
     </row>
     <row r="331">
@@ -5715,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>20.44454523800446</v>
+        <v>28.38498368035059</v>
       </c>
     </row>
     <row r="332">
@@ -5731,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>25.28483925959621</v>
+        <v>26.39816464695118</v>
       </c>
     </row>
     <row r="333">
@@ -5747,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>26.89710552216126</v>
+        <v>26.77753621449802</v>
       </c>
     </row>
     <row r="334">
@@ -5763,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>25.18236396032823</v>
+        <v>29.88304510226989</v>
       </c>
     </row>
     <row r="335">
@@ -5779,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>27.54720478718497</v>
+        <v>28.41186679923126</v>
       </c>
     </row>
     <row r="336">
@@ -5795,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>31.28168860546676</v>
+        <v>28.07454713302252</v>
       </c>
     </row>
     <row r="337">
@@ -5811,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>20.36739334265722</v>
+        <v>27.43072243577382</v>
       </c>
     </row>
     <row r="338">
@@ -5827,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>25.70925062098112</v>
+        <v>29.2026384638177</v>
       </c>
     </row>
     <row r="339">
@@ -5843,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>31.04537599909696</v>
+        <v>30.93257902903899</v>
       </c>
     </row>
     <row r="340">
@@ -5859,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>17.94114648715123</v>
+        <v>23.61147112517853</v>
       </c>
     </row>
     <row r="341">
@@ -5875,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>29.87507626416812</v>
+        <v>27.10261274250927</v>
       </c>
     </row>
     <row r="342">
@@ -5891,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>29.04836818107147</v>
+        <v>29.29310240126282</v>
       </c>
     </row>
     <row r="343">
@@ -5907,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>26.53135022585028</v>
+        <v>20.01223748859628</v>
       </c>
     </row>
     <row r="344">
@@ -5923,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>25.8352987395026</v>
+        <v>28.78274854010469</v>
       </c>
     </row>
     <row r="345">
@@ -5939,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>31.0662557218727</v>
+        <v>30.69514604979343</v>
       </c>
     </row>
     <row r="346">
@@ -5955,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>18.32935856087592</v>
+        <v>23.35133421147205</v>
       </c>
     </row>
     <row r="347">
@@ -5971,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>29.46362519914022</v>
+        <v>27.0736914193375</v>
       </c>
     </row>
     <row r="348">
@@ -5987,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>28.57461191095105</v>
+        <v>28.22776273769819</v>
       </c>
     </row>
     <row r="349">
@@ -6003,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>26.56042484895995</v>
+        <v>20.27420720390161</v>
       </c>
     </row>
     <row r="350">
@@ -6019,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>25.89053263547772</v>
+        <v>28.89955633159597</v>
       </c>
     </row>
     <row r="351">
@@ -6035,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>30.80860381826332</v>
+        <v>30.9178771860367</v>
       </c>
     </row>
     <row r="352">
@@ -6051,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>18.36247823730911</v>
+        <v>23.34727099198109</v>
       </c>
     </row>
     <row r="353">
@@ -6067,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>29.23756588870105</v>
+        <v>26.82800261414788</v>
       </c>
     </row>
     <row r="354">
@@ -6083,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>28.80806242424442</v>
+        <v>28.67556020763989</v>
       </c>
     </row>
     <row r="355">
@@ -6099,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>26.24825354044698</v>
+        <v>20.07735300467299</v>
       </c>
     </row>
     <row r="356">
@@ -6115,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>25.00755681022564</v>
+        <v>29.2631714976385</v>
       </c>
     </row>
     <row r="357">
@@ -6131,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>31.28401714643574</v>
+        <v>31.00555125030442</v>
       </c>
     </row>
     <row r="358">
@@ -6147,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>18.13942056815578</v>
+        <v>23.03269341063235</v>
       </c>
     </row>
     <row r="359">
@@ -6163,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>29.31053961350003</v>
+        <v>27.21905461889997</v>
       </c>
     </row>
     <row r="360">
@@ -6179,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>28.73012638344805</v>
+        <v>28.67083580515452</v>
       </c>
     </row>
     <row r="361">
@@ -6195,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>26.74211133740918</v>
+        <v>20.13139963433389</v>
       </c>
     </row>
     <row r="362">
@@ -6211,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>25.58318700817073</v>
+        <v>29.25018477161604</v>
       </c>
     </row>
     <row r="363">
@@ -6227,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>31.10786637441846</v>
+        <v>30.39426021910589</v>
       </c>
     </row>
     <row r="364">
@@ -6243,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>18.09932546634991</v>
+        <v>23.13320307159</v>
       </c>
     </row>
     <row r="365">
@@ -6259,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>29.55274479880319</v>
+        <v>26.75813015836751</v>
       </c>
     </row>
     <row r="366">
@@ -6275,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>28.70739159525363</v>
+        <v>29.38998153818003</v>
       </c>
     </row>
     <row r="367">
@@ -6291,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>26.45815526763996</v>
+        <v>20.29944748511542</v>
       </c>
     </row>
     <row r="368">
@@ -6307,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>25.48432953205291</v>
+        <v>29.07663459430304</v>
       </c>
     </row>
     <row r="369">
@@ -6323,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>30.85270623125793</v>
+        <v>30.77792392441868</v>
       </c>
     </row>
     <row r="370">
@@ -6339,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>18.10273162168489</v>
+        <v>23.23586319089648</v>
       </c>
     </row>
     <row r="371">
@@ -6355,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>29.53561506979057</v>
+        <v>27.02270179610979</v>
       </c>
     </row>
     <row r="372">
@@ -6371,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>28.56982167040205</v>
+        <v>29.00070095750247</v>
       </c>
     </row>
     <row r="373">
@@ -6387,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>26.82842507941692</v>
+        <v>20.44600737647483</v>
       </c>
     </row>
     <row r="374">
@@ -6403,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>25.99423225347372</v>
+        <v>29.12618606751351</v>
       </c>
     </row>
     <row r="375">
@@ -6419,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>31.16976283595466</v>
+        <v>30.53535948939236</v>
       </c>
     </row>
     <row r="376">
@@ -6435,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>18.18381121932124</v>
+        <v>23.1980104275224</v>
       </c>
     </row>
     <row r="377">
@@ -6451,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>29.51996854342711</v>
+        <v>26.4591271314441</v>
       </c>
     </row>
     <row r="378">
@@ -6467,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>29.18747236785293</v>
+        <v>28.38694178501519</v>
       </c>
     </row>
     <row r="379">
@@ -6483,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>27.08725932148264</v>
+        <v>20.56966181583805</v>
       </c>
     </row>
     <row r="380">
@@ -6499,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>25.63566092691616</v>
+        <v>29.76319652362181</v>
       </c>
     </row>
     <row r="381">
@@ -6515,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>31.00726105732797</v>
+        <v>30.63572151207531</v>
       </c>
     </row>
     <row r="382">
@@ -6531,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>18.23378389607457</v>
+        <v>23.39611157388414</v>
       </c>
     </row>
     <row r="383">
@@ -6547,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>29.76416482740661</v>
+        <v>27.16684045577297</v>
       </c>
     </row>
     <row r="384">
@@ -6563,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>28.73487945256259</v>
+        <v>29.71112215511457</v>
       </c>
     </row>
     <row r="385">
@@ -6579,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>26.74993110787512</v>
+        <v>20.51947910913864</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.0853187380475</v>
+        <v>25.23335715171726</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.12369601522129</v>
+        <v>25.46992865686047</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.26532160975045</v>
+        <v>34.93468229650791</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26.85861460724102</v>
+        <v>31.30386906122607</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.5733656442835</v>
+        <v>28.48666337781285</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.26613509053244</v>
+        <v>29.41580787946376</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.89369070365238</v>
+        <v>24.84160037310648</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.87845444676072</v>
+        <v>25.00919781856836</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.21995466117444</v>
+        <v>35.12129042543752</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.03054725563269</v>
+        <v>31.07070826056691</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.49678574744939</v>
+        <v>29.03081505331511</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28.43509237705367</v>
+        <v>29.61206275082664</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30.07374912477554</v>
+        <v>25.05767996202252</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.04631774045898</v>
+        <v>25.45861305914355</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.74079508798118</v>
+        <v>34.58926894319338</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26.91463161036991</v>
+        <v>30.86583863261803</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.98607992743867</v>
+        <v>28.6624216040443</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29.08474204068694</v>
+        <v>29.46401154024958</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.93879149633678</v>
+        <v>25.12843316653775</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23.133034898786</v>
+        <v>25.4383986021032</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.25446368892001</v>
+        <v>34.99587529012279</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.60714080600722</v>
+        <v>30.45041861018985</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.28887278626872</v>
+        <v>29.07101013025882</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28.59897775964668</v>
+        <v>30.22798446495321</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.23377488268549</v>
+        <v>24.98902643687655</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22.85375110243023</v>
+        <v>25.14790733690464</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27.64638430427586</v>
+        <v>34.82565960089721</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.54436650136627</v>
+        <v>30.65663566016515</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.13337343288733</v>
+        <v>29.58069035551913</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.00731013014455</v>
+        <v>30.09076555918005</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.69936687992453</v>
+        <v>24.99639427650352</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>22.93287955853662</v>
+        <v>25.42055235577398</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>27.29109635655066</v>
+        <v>35.11795421812519</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.78622505916637</v>
+        <v>30.82431857822856</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>27.53552531550904</v>
+        <v>29.37655005792929</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28.40499949542222</v>
+        <v>29.91054927780932</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>29.6778391801997</v>
+        <v>25.32705738772799</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>23.1727144963326</v>
+        <v>25.56967678482805</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>27.01325632417877</v>
+        <v>34.59100325086078</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27.33903938453419</v>
+        <v>31.10508138873882</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27.75016405294309</v>
+        <v>28.89899725917272</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28.29411863393847</v>
+        <v>30.35783586434798</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30.24051967523399</v>
+        <v>24.83617798430596</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>22.77960732642177</v>
+        <v>25.62656555963795</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27.32594199225768</v>
+        <v>35.01126504540986</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>27.27367557567923</v>
+        <v>30.77417250969077</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27.51963325171168</v>
+        <v>29.23163587441</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28.43794683967966</v>
+        <v>29.58622555043402</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>32.07303485763677</v>
+        <v>28.41964390140805</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30.84688142834338</v>
+        <v>23.43870875021423</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>22.44592923236874</v>
+        <v>20.2959566174661</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26.77590993869613</v>
+        <v>28.54759791769133</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31.15555976851631</v>
+        <v>28.00559308473906</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>29.89314116689913</v>
+        <v>23.03869295060715</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>32.07003102410232</v>
+        <v>29.4684370813054</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>30.71362376141913</v>
+        <v>23.70177285977342</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>22.57250208966166</v>
+        <v>20.06776482687176</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.1972255427317</v>
+        <v>28.65593796623897</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>31.08462456199494</v>
+        <v>28.38839734738955</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>29.59171622733891</v>
+        <v>22.76727955603238</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>32.58675798974242</v>
+        <v>29.10399617042023</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30.75261314439343</v>
+        <v>23.69653537789222</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>22.45630349820185</v>
+        <v>20.53108890954398</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>27.31235595200049</v>
+        <v>28.50359251136072</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30.69169950130432</v>
+        <v>28.20520384760701</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30.03921361819298</v>
+        <v>22.68120037413499</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>32.36053216632335</v>
+        <v>28.23143125833531</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30.35639330082552</v>
+        <v>23.60232054006225</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>22.9459986499997</v>
+        <v>20.13721319937091</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>27.24621017196735</v>
+        <v>28.3315121273257</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>31.24857789629164</v>
+        <v>28.66484778034235</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30.36995805017136</v>
+        <v>22.14266990407861</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>31.91139920571509</v>
+        <v>28.83118402355754</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30.37688390136735</v>
+        <v>23.60953438151771</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>22.52489125549262</v>
+        <v>20.37433955098065</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.9128417096471</v>
+        <v>28.64719803863677</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30.96989355208163</v>
+        <v>28.37188797918453</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>29.90630506594851</v>
+        <v>22.46965337209506</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>32.07841172142162</v>
+        <v>28.51298884272223</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30.86076514406685</v>
+        <v>23.86978782684061</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>22.73000660611551</v>
+        <v>20.11888037848789</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.52861026891005</v>
+        <v>28.61092501904773</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30.91176311031762</v>
+        <v>28.37157661359835</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>30.61536224233168</v>
+        <v>22.63190527770304</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>32.19004896545693</v>
+        <v>28.40286825298632</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30.34522911157405</v>
+        <v>23.57839696718032</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>22.48366936818038</v>
+        <v>20.18289793436576</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.2651204035143</v>
+        <v>28.45708400576851</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>30.92453070714119</v>
+        <v>28.55993378419026</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>30.01743117264935</v>
+        <v>22.73956223359943</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>32.14128685154849</v>
+        <v>28.71745007840202</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30.58529316266471</v>
+        <v>23.25484214130603</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>22.53460041367748</v>
+        <v>20.14537880541877</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>26.72316359096767</v>
+        <v>28.45602822448586</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30.85539838633474</v>
+        <v>28.46490860843006</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30.05987245345765</v>
+        <v>22.61452790453408</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>27.66950683805296</v>
+        <v>34.28740276267906</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>27.13782391973364</v>
+        <v>34.12306513337914</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>21.7228483936089</v>
+        <v>20.09543421849488</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>24.74560458124206</v>
+        <v>28.69823284502678</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>32.1508755266154</v>
+        <v>23.91953441838898</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>31.33743567651315</v>
+        <v>31.74694195463112</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>27.62646636716737</v>
+        <v>33.51353444447196</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>27.1660648574326</v>
+        <v>33.75119881150028</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>21.76288084093663</v>
+        <v>19.95932019402358</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>24.78885832333376</v>
+        <v>28.68060809814158</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>32.78889305319687</v>
+        <v>24.11665537178206</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>31.61906377743652</v>
+        <v>31.46470659543133</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>27.23001475995352</v>
+        <v>34.15737002190569</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>27.22243909200669</v>
+        <v>33.99654505462493</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>21.79698051122132</v>
+        <v>20.30192046346335</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>24.77727288241</v>
+        <v>28.18251801554142</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>32.60464645942106</v>
+        <v>24.51805647132269</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>32.49483021700793</v>
+        <v>31.91116952950478</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>27.7680198336144</v>
+        <v>33.77699451092729</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>27.79221006186055</v>
+        <v>34.02043998895483</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>21.8921716847523</v>
+        <v>20.45773209563065</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>24.8111934441087</v>
+        <v>28.29278020018155</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>32.33531176172219</v>
+        <v>24.09002670990119</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>31.52681254180862</v>
+        <v>31.23692906987641</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>27.39701461809451</v>
+        <v>33.95590081017612</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27.41507674545921</v>
+        <v>34.50101809943953</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>21.58004109099569</v>
+        <v>19.83293816867709</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>24.67080393674179</v>
+        <v>28.42773457792295</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>33.1883966328481</v>
+        <v>24.27943184917562</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30.70508122922451</v>
+        <v>31.39825599773055</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>27.79987385755037</v>
+        <v>33.76266228809074</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27.03697804640046</v>
+        <v>33.9787996787007</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>21.5829537906816</v>
+        <v>19.7419252255787</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>24.91905454203809</v>
+        <v>29.32113626650277</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>32.45842834817261</v>
+        <v>23.93511645105033</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>30.95211692543657</v>
+        <v>31.34401745625629</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.41289653274493</v>
+        <v>33.89782222602247</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>27.66690937920993</v>
+        <v>34.36790722144909</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>21.52691145292214</v>
+        <v>19.84339477177494</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>24.70397984009355</v>
+        <v>28.51227334448122</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>32.45235986805462</v>
+        <v>24.22061216619059</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>31.0854546885606</v>
+        <v>31.0552922919897</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>28.20234613567843</v>
+        <v>33.50690820456013</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.65435679439516</v>
+        <v>33.51566158705909</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>21.24613548561328</v>
+        <v>20.22744988112534</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>24.69658359988992</v>
+        <v>29.22135188795649</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>32.22290997000602</v>
+        <v>24.43750045461823</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>31.55605684267644</v>
+        <v>31.03120017379369</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>28.5629946491987</v>
+        <v>31.50238836791862</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>30.77454194026616</v>
+        <v>31.81414285832061</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>27.54879943231923</v>
+        <v>29.6891599603027</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>26.42043769967777</v>
+        <v>23.68906711325857</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.71108443900398</v>
+        <v>26.47500798836797</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>31.89130775774083</v>
+        <v>28.83237606906519</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>28.65442833239878</v>
+        <v>31.35003600513835</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>30.60860208239184</v>
+        <v>31.9160154254459</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>27.89429822245935</v>
+        <v>29.98357918337848</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>26.29974423851887</v>
+        <v>24.15147915207519</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>30.69225129262015</v>
+        <v>26.19674276870598</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>32.2920432197155</v>
+        <v>28.76877339832027</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>29.40216425950368</v>
+        <v>31.70917376828989</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>31.12799354698901</v>
+        <v>31.23553279632959</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>26.99391540885022</v>
+        <v>29.43057271170418</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>26.06682603775835</v>
+        <v>23.86103926721848</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>31.4779958449378</v>
+        <v>26.40647045400232</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>31.77190010906777</v>
+        <v>28.87231150832085</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>28.918951456341</v>
+        <v>31.59014375181805</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>31.04855603023831</v>
+        <v>31.35997175368312</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>27.15630532847723</v>
+        <v>29.9121498962737</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>26.17807281493502</v>
+        <v>23.61017261117837</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>30.07666522131515</v>
+        <v>25.70479520540017</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>31.67055554209665</v>
+        <v>28.20281802971987</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>28.7184533199484</v>
+        <v>31.68616914986581</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>30.42545146191644</v>
+        <v>31.27751792582732</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>27.85783064738067</v>
+        <v>29.62543359240186</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>25.81905825001109</v>
+        <v>23.71624201396563</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>30.94740256620453</v>
+        <v>25.82399737515556</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>32.04017742706655</v>
+        <v>28.31957314706055</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>29.2061300995677</v>
+        <v>31.92265363637207</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>30.36750453441212</v>
+        <v>32.24010956406255</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>27.72920810796261</v>
+        <v>29.38008152815036</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>26.19634510079635</v>
+        <v>23.01173700119486</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>30.77909283381314</v>
+        <v>25.97179134443432</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>32.14620806212114</v>
+        <v>28.76634642011519</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>28.84848226405982</v>
+        <v>31.09843303468297</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>30.62496594179443</v>
+        <v>30.599455710758</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>27.42951351477685</v>
+        <v>29.47345795032039</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>26.09273693554986</v>
+        <v>23.34265573548663</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>31.1194727601923</v>
+        <v>26.48050425775492</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>32.21021345097125</v>
+        <v>28.86982497122615</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>29.24780345545017</v>
+        <v>31.74510098249836</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>30.42852249433754</v>
+        <v>31.75696785415209</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>27.99505306182169</v>
+        <v>29.59576734251451</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>25.68234135450083</v>
+        <v>23.80877373370624</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>31.03700565402474</v>
+        <v>26.03094873742024</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>32.18659436457719</v>
+        <v>28.59134430520947</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>28.97730019028065</v>
+        <v>31.94041686146799</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>32.17936589084081</v>
+        <v>29.34137456138508</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>15.7501461715677</v>
+        <v>24.92168243634886</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>30.1519411868662</v>
+        <v>30.82055235509403</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>30.0827927034048</v>
+        <v>33.4079931387621</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>25.04486042480135</v>
+        <v>30.26181573104521</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>28.99926805443888</v>
+        <v>32.24879226089242</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>32.15663116474247</v>
+        <v>29.32581279571836</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>15.92497788925971</v>
+        <v>24.32438949067328</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>30.39444284497853</v>
+        <v>30.88200890542878</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>30.507122558296</v>
+        <v>33.91222569084454</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>24.99023254966304</v>
+        <v>30.29583849280444</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>28.65655722203655</v>
+        <v>32.39407587928497</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>32.19961000112582</v>
+        <v>29.14871059422359</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>15.90093939961181</v>
+        <v>24.89023201860716</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>30.48627730236517</v>
+        <v>30.53266080267829</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>30.25481614385098</v>
+        <v>33.75429149004402</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>24.86300826459261</v>
+        <v>30.27752222236737</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>29.26529986985653</v>
+        <v>32.83543016227583</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>32.1894454916311</v>
+        <v>29.75635010869831</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>15.86934244140877</v>
+        <v>24.18443655309791</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>30.24005995544189</v>
+        <v>30.84074892394237</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>30.1952683884298</v>
+        <v>33.1899832543601</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>25.10674016284441</v>
+        <v>30.04198401344856</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>29.13461765723405</v>
+        <v>32.24397324028452</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>32.64442480970493</v>
+        <v>29.10804956013337</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>15.98903773708224</v>
+        <v>24.35777106740808</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>30.30769145498891</v>
+        <v>30.44223554180371</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>30.46750795630783</v>
+        <v>33.53471982349205</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>24.75682008606106</v>
+        <v>29.46168928892019</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>28.98977593450654</v>
+        <v>32.29015100671702</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>32.33886061093406</v>
+        <v>28.79556053504204</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>15.79830296147626</v>
+        <v>24.30172163095502</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>30.48166748876465</v>
+        <v>30.41049940748991</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>30.01353828839505</v>
+        <v>33.30863337213201</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>25.35349209701874</v>
+        <v>29.63260214758923</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>28.60540465286982</v>
+        <v>31.74996877707522</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>31.98783579441977</v>
+        <v>29.20881085252847</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>15.96577866481706</v>
+        <v>24.74044778712073</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>30.54121131398233</v>
+        <v>31.07607515570463</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>30.45000698383927</v>
+        <v>33.59330327064729</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>24.98991384848164</v>
+        <v>29.29774000950494</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>28.89256564630306</v>
+        <v>32.11892829662923</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>32.09046227818327</v>
+        <v>29.32458594476672</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>15.79495832299273</v>
+        <v>24.27334278894775</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.09613802764359</v>
+        <v>30.3992451760515</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>30.55622356415909</v>
+        <v>34.11650266276052</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>24.79735129227493</v>
+        <v>30.08493953417796</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>29.02451536523277</v>
+        <v>26.64475613970544</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>22.36270474569161</v>
+        <v>30.18179312007887</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>25.24710414769315</v>
+        <v>31.01927137590491</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>28.83643555795685</v>
+        <v>31.17584070716758</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>34.15056137677244</v>
+        <v>31.74401294813208</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>24.03717928657334</v>
+        <v>34.52127146568227</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>29.3377984289354</v>
+        <v>27.90251226544275</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>22.32107531592501</v>
+        <v>29.58254098552658</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>25.02484515905266</v>
+        <v>31.72970030532386</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>29.0672094852888</v>
+        <v>30.97382776612824</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>33.93505337503788</v>
+        <v>31.36200703356615</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>23.64125398313965</v>
+        <v>34.62330058980275</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>29.0558456028002</v>
+        <v>27.70360356559018</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>22.38692058250046</v>
+        <v>29.91312979623033</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>25.22145199606594</v>
+        <v>31.34793725093935</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>29.42776725204962</v>
+        <v>30.40139560316358</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>34.72900592267152</v>
+        <v>31.95996709702643</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>23.94039489463883</v>
+        <v>34.54622259307232</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>29.26054094834307</v>
+        <v>27.36593120144549</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>22.20989151065052</v>
+        <v>29.79919858743531</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>25.13862482788148</v>
+        <v>31.44807177754928</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>28.91620443972791</v>
+        <v>30.72173322923711</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>34.54480601747952</v>
+        <v>31.10579388970011</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>23.78038654071459</v>
+        <v>34.43649178723095</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>29.41809875462659</v>
+        <v>27.08731291118906</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>22.7786740566631</v>
+        <v>30.09180771794482</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>25.11593376917311</v>
+        <v>31.14893077692459</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>29.11641125899098</v>
+        <v>31.33011623444187</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>34.6713241225988</v>
+        <v>31.02353050660958</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>23.88253851028252</v>
+        <v>34.43218007400142</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>29.33168939578223</v>
+        <v>27.5901602439873</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>22.43763211993449</v>
+        <v>30.32082980351497</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>25.16783861203077</v>
+        <v>31.62806546801916</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>28.7757430184253</v>
+        <v>30.77041721540098</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>34.44212188971942</v>
+        <v>31.13148217863998</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>24.09815989481555</v>
+        <v>34.01117400407948</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>29.69079948207868</v>
+        <v>27.82372603935761</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>22.65001759793227</v>
+        <v>29.93761380031195</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>25.68466032383</v>
+        <v>31.55689112413804</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>28.7773850577043</v>
+        <v>30.3176188083776</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>34.73405424946419</v>
+        <v>31.37923489371287</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>24.02270926287277</v>
+        <v>34.25939281101892</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>29.90697630509682</v>
+        <v>27.5402357300516</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>22.25346687849758</v>
+        <v>29.53330474760273</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>24.93214602647758</v>
+        <v>31.56306134091226</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>28.82609184133769</v>
+        <v>30.71712059351419</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>33.70234663165332</v>
+        <v>31.55193412631351</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>23.85267668671973</v>
+        <v>34.48554648310837</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>26.45301894287697</v>
+        <v>29.15858299269645</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>26.63507762620971</v>
+        <v>28.67070464614751</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>29.67112573435474</v>
+        <v>26.57315175367366</v>
       </c>
     </row>
     <row r="293">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>29.46310115289606</v>
+        <v>29.72462402186491</v>
       </c>
     </row>
     <row r="294">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>28.68074163836922</v>
+        <v>30.58033590290009</v>
       </c>
     </row>
     <row r="295">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>27.84019991018853</v>
+        <v>21.65811509979481</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>26.41589280984012</v>
+        <v>29.29386661644348</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>26.72590657652815</v>
+        <v>28.54930303116323</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>29.1796743985436</v>
+        <v>26.2356143640987</v>
       </c>
     </row>
     <row r="299">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>29.45017019633031</v>
+        <v>29.45754785342478</v>
       </c>
     </row>
     <row r="300">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>28.74580681175474</v>
+        <v>31.29405157222848</v>
       </c>
     </row>
     <row r="301">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>27.8703656288721</v>
+        <v>21.93977479129002</v>
       </c>
     </row>
     <row r="302">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>26.1987262290957</v>
+        <v>28.97692574051912</v>
       </c>
     </row>
     <row r="303">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>26.95514372273376</v>
+        <v>29.36071076927728</v>
       </c>
     </row>
     <row r="304">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>29.5361987486131</v>
+        <v>25.95816821413532</v>
       </c>
     </row>
     <row r="305">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>29.27848581201093</v>
+        <v>29.77263806063981</v>
       </c>
     </row>
     <row r="306">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>27.95773102070302</v>
+        <v>30.62973109168695</v>
       </c>
     </row>
     <row r="307">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>27.83390753567346</v>
+        <v>21.76672364932406</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>26.65676627909538</v>
+        <v>28.88487790708302</v>
       </c>
     </row>
     <row r="309">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>26.60757480459009</v>
+        <v>28.98361381221733</v>
       </c>
     </row>
     <row r="310">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>29.43698359191132</v>
+        <v>26.22272207994123</v>
       </c>
     </row>
     <row r="311">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>29.10063444108391</v>
+        <v>29.1162470900519</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>28.10740074437057</v>
+        <v>30.68477032364282</v>
       </c>
     </row>
     <row r="313">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>27.96187425167716</v>
+        <v>22.00985183060646</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>26.68743379559405</v>
+        <v>29.42736511351247</v>
       </c>
     </row>
     <row r="315">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>26.73189569886224</v>
+        <v>28.23136871466429</v>
       </c>
     </row>
     <row r="316">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>29.78049326423044</v>
+        <v>26.31745020028302</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>28.59525095593398</v>
+        <v>29.46394097276065</v>
       </c>
     </row>
     <row r="318">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>27.97486651654892</v>
+        <v>30.51263819535131</v>
       </c>
     </row>
     <row r="319">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>28.35951476904194</v>
+        <v>22.0297097228649</v>
       </c>
     </row>
     <row r="320">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>26.74394807625156</v>
+        <v>29.22395750863224</v>
       </c>
     </row>
     <row r="321">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>26.39601968269633</v>
+        <v>28.52114999669924</v>
       </c>
     </row>
     <row r="322">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>30.02874495700152</v>
+        <v>26.44654639262599</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>28.95395679325184</v>
+        <v>29.51640768266355</v>
       </c>
     </row>
     <row r="324">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>28.74576620242208</v>
+        <v>30.49071147122902</v>
       </c>
     </row>
     <row r="325">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>28.02064934077672</v>
+        <v>21.60029033034041</v>
       </c>
     </row>
     <row r="326">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>27.2046685059067</v>
+        <v>28.83042859889686</v>
       </c>
     </row>
     <row r="327">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>27.06191458416295</v>
+        <v>28.09666976544536</v>
       </c>
     </row>
     <row r="328">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>29.4964493903923</v>
+        <v>26.21353911389393</v>
       </c>
     </row>
     <row r="329">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>29.20148631410503</v>
+        <v>28.87621959405397</v>
       </c>
     </row>
     <row r="330">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>28.59407533873767</v>
+        <v>31.11229844559902</v>
       </c>
     </row>
     <row r="331">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>28.38498368035059</v>
+        <v>22.19517419052199</v>
       </c>
     </row>
     <row r="332">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>26.39816464695118</v>
+        <v>28.72392435017658</v>
       </c>
     </row>
     <row r="333">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>26.77753621449802</v>
+        <v>28.83450859263097</v>
       </c>
     </row>
     <row r="334">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>29.88304510226989</v>
+        <v>26.185706576563</v>
       </c>
     </row>
     <row r="335">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>28.41186679923126</v>
+        <v>29.30833248782836</v>
       </c>
     </row>
     <row r="336">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>28.07454713302252</v>
+        <v>30.47253741415443</v>
       </c>
     </row>
     <row r="337">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>27.43072243577382</v>
+        <v>21.76520298408697</v>
       </c>
     </row>
     <row r="338">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>29.2026384638177</v>
+        <v>23.77062729008717</v>
       </c>
     </row>
     <row r="339">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>30.93257902903899</v>
+        <v>28.89563336957069</v>
       </c>
     </row>
     <row r="340">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>23.61147112517853</v>
+        <v>23.45658256053971</v>
       </c>
     </row>
     <row r="341">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>27.10261274250927</v>
+        <v>27.51216146148868</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>29.29310240126282</v>
+        <v>28.99623793860649</v>
       </c>
     </row>
     <row r="343">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>20.01223748859628</v>
+        <v>19.43133939793849</v>
       </c>
     </row>
     <row r="344">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>28.78274854010469</v>
+        <v>24.25343228011144</v>
       </c>
     </row>
     <row r="345">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>30.69514604979343</v>
+        <v>29.06398273638761</v>
       </c>
     </row>
     <row r="346">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>23.35133421147205</v>
+        <v>23.77949690433818</v>
       </c>
     </row>
     <row r="347">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>27.0736914193375</v>
+        <v>27.09329394986443</v>
       </c>
     </row>
     <row r="348">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>28.22776273769819</v>
+        <v>28.81188752553843</v>
       </c>
     </row>
     <row r="349">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>20.27420720390161</v>
+        <v>18.99452417509858</v>
       </c>
     </row>
     <row r="350">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>28.89955633159597</v>
+        <v>24.62774419881435</v>
       </c>
     </row>
     <row r="351">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>30.9178771860367</v>
+        <v>29.12855262599962</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>23.34727099198109</v>
+        <v>23.56955445817271</v>
       </c>
     </row>
     <row r="353">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>26.82800261414788</v>
+        <v>27.1935962749658</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>28.67556020763989</v>
+        <v>28.52805611967844</v>
       </c>
     </row>
     <row r="355">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>20.07735300467299</v>
+        <v>19.12287105559075</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>29.2631714976385</v>
+        <v>24.45251118925986</v>
       </c>
     </row>
     <row r="357">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>31.00555125030442</v>
+        <v>29.18741441097979</v>
       </c>
     </row>
     <row r="358">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>23.03269341063235</v>
+        <v>23.35107729430423</v>
       </c>
     </row>
     <row r="359">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>27.21905461889997</v>
+        <v>27.14979966602197</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>28.67083580515452</v>
+        <v>28.2986289289807</v>
       </c>
     </row>
     <row r="361">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>20.13139963433389</v>
+        <v>19.00334071378777</v>
       </c>
     </row>
     <row r="362">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>29.25018477161604</v>
+        <v>23.7632170753158</v>
       </c>
     </row>
     <row r="363">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>30.39426021910589</v>
+        <v>29.38015199249218</v>
       </c>
     </row>
     <row r="364">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>23.13320307159</v>
+        <v>23.78987438534529</v>
       </c>
     </row>
     <row r="365">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>26.75813015836751</v>
+        <v>27.21446866396735</v>
       </c>
     </row>
     <row r="366">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>29.38998153818003</v>
+        <v>27.95180424295715</v>
       </c>
     </row>
     <row r="367">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>20.29944748511542</v>
+        <v>18.9257443001351</v>
       </c>
     </row>
     <row r="368">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>29.07663459430304</v>
+        <v>24.29000917741612</v>
       </c>
     </row>
     <row r="369">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>30.77792392441868</v>
+        <v>29.19174474612668</v>
       </c>
     </row>
     <row r="370">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>23.23586319089648</v>
+        <v>23.7279236498624</v>
       </c>
     </row>
     <row r="371">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>27.02270179610979</v>
+        <v>27.04639358419827</v>
       </c>
     </row>
     <row r="372">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>29.00070095750247</v>
+        <v>29.0890170783573</v>
       </c>
     </row>
     <row r="373">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>20.44600737647483</v>
+        <v>18.82668689332268</v>
       </c>
     </row>
     <row r="374">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>29.12618606751351</v>
+        <v>24.54600986429595</v>
       </c>
     </row>
     <row r="375">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>30.53535948939236</v>
+        <v>29.57692781307704</v>
       </c>
     </row>
     <row r="376">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>23.1980104275224</v>
+        <v>23.42235197082717</v>
       </c>
     </row>
     <row r="377">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>26.4591271314441</v>
+        <v>27.20897938517186</v>
       </c>
     </row>
     <row r="378">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>28.38694178501519</v>
+        <v>28.67182686986325</v>
       </c>
     </row>
     <row r="379">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>20.56966181583805</v>
+        <v>19.06456408215596</v>
       </c>
     </row>
     <row r="380">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>29.76319652362181</v>
+        <v>24.12799090111627</v>
       </c>
     </row>
     <row r="381">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>30.63572151207531</v>
+        <v>29.00829040657237</v>
       </c>
     </row>
     <row r="382">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>23.39611157388414</v>
+        <v>23.70454565117775</v>
       </c>
     </row>
     <row r="383">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>27.16684045577297</v>
+        <v>27.85473664400557</v>
       </c>
     </row>
     <row r="384">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>29.71112215511457</v>
+        <v>27.85454528482234</v>
       </c>
     </row>
     <row r="385">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>20.51947910913864</v>
+        <v>18.97014512744204</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.23335715171726</v>
+        <v>27.55976937021038</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.46992865686047</v>
+        <v>31.19391485692695</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.93468229650791</v>
+        <v>30.50411142857464</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.30386906122607</v>
+        <v>29.83195581255654</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.48666337781285</v>
+        <v>28.34655518807741</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.41580787946376</v>
+        <v>21.00142410743999</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.84160037310648</v>
+        <v>26.96511451945375</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.00919781856836</v>
+        <v>31.22942729822399</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35.12129042543752</v>
+        <v>30.27529891126438</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.07070826056691</v>
+        <v>29.29234847022125</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.03081505331511</v>
+        <v>28.13808391377904</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.61206275082664</v>
+        <v>21.09594887484221</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.05767996202252</v>
+        <v>27.0959009507392</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.45861305914355</v>
+        <v>30.86297802804966</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>34.58926894319338</v>
+        <v>29.98057436330386</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.86583863261803</v>
+        <v>29.28406668117323</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.6624216040443</v>
+        <v>28.02487232170109</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29.46401154024958</v>
+        <v>20.91214477264514</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25.12843316653775</v>
+        <v>27.41645957588015</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.4383986021032</v>
+        <v>30.88200046194956</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.99587529012279</v>
+        <v>30.18054868518402</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30.45041861018985</v>
+        <v>29.77265615819004</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.07101013025882</v>
+        <v>28.26630438614874</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30.22798446495321</v>
+        <v>20.53970039707613</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24.98902643687655</v>
+        <v>26.92314748106145</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25.14790733690464</v>
+        <v>31.78050225524007</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34.82565960089721</v>
+        <v>30.4877456639553</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>30.65663566016515</v>
+        <v>28.97607434865328</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.58069035551913</v>
+        <v>28.28298061534533</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.09076555918005</v>
+        <v>21.10563860051205</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>24.99639427650352</v>
+        <v>27.13750021827272</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>25.42055235577398</v>
+        <v>30.99884885382235</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>35.11795421812519</v>
+        <v>30.42053452006191</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>30.82431857822856</v>
+        <v>29.81673879041724</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29.37655005792929</v>
+        <v>28.23141444258165</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29.91054927780932</v>
+        <v>21.37982918826821</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>25.32705738772799</v>
+        <v>27.53783730613607</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>25.56967678482805</v>
+        <v>31.66865875619099</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>34.59100325086078</v>
+        <v>30.04491625977233</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.10508138873882</v>
+        <v>29.5673613848153</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.89899725917272</v>
+        <v>28.14962044306536</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>30.35783586434798</v>
+        <v>20.76648190113847</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>24.83617798430596</v>
+        <v>27.04125189036933</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>25.62656555963795</v>
+        <v>30.90920129081247</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>35.01126504540986</v>
+        <v>30.54302189484886</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30.77417250969077</v>
+        <v>29.58438695315113</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.23163587441</v>
+        <v>28.27936264515174</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>29.58622555043402</v>
+        <v>20.85538062751549</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28.41964390140805</v>
+        <v>27.07412811556643</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>23.43870875021423</v>
+        <v>25.79226621969717</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20.2959566174661</v>
+        <v>27.58054206167661</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28.54759791769133</v>
+        <v>30.76394835233369</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>28.00559308473906</v>
+        <v>32.08372004960465</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>23.03869295060715</v>
+        <v>22.37243627322901</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29.4684370813054</v>
+        <v>27.18295761201992</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>23.70177285977342</v>
+        <v>26.42251190955269</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>20.06776482687176</v>
+        <v>27.88968668208256</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.65593796623897</v>
+        <v>30.76420479142753</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>28.38839734738955</v>
+        <v>32.39599036937543</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.76727955603238</v>
+        <v>22.97134986153462</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>29.10399617042023</v>
+        <v>27.12759641311545</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>23.69653537789222</v>
+        <v>26.19241765616201</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20.53108890954398</v>
+        <v>27.62280090456441</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>28.50359251136072</v>
+        <v>30.54720235765415</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>28.20520384760701</v>
+        <v>32.07521418958203</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.68120037413499</v>
+        <v>22.30731590624156</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>28.23143125833531</v>
+        <v>27.12229407183639</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>23.60232054006225</v>
+        <v>26.75151325562631</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>20.13721319937091</v>
+        <v>27.97546380117557</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>28.3315121273257</v>
+        <v>30.7514567587041</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.66484778034235</v>
+        <v>31.90836050783833</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.14266990407861</v>
+        <v>22.13249422626382</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.83118402355754</v>
+        <v>27.34956941738156</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>23.60953438151771</v>
+        <v>26.59049500467742</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>20.37433955098065</v>
+        <v>27.70877669071917</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>28.64719803863677</v>
+        <v>30.84797124675926</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>28.37188797918453</v>
+        <v>32.57190754673525</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22.46965337209506</v>
+        <v>22.38419599878911</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28.51298884272223</v>
+        <v>27.33144560758414</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>23.86978782684061</v>
+        <v>26.18911744028786</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>20.11888037848789</v>
+        <v>27.64807400833077</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>28.61092501904773</v>
+        <v>30.53263433476529</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>28.37157661359835</v>
+        <v>32.35997454469751</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>22.63190527770304</v>
+        <v>22.61373659716448</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>28.40286825298632</v>
+        <v>27.2110176800215</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>23.57839696718032</v>
+        <v>26.02242566852274</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>20.18289793436576</v>
+        <v>27.66236004408714</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>28.45708400576851</v>
+        <v>30.68063990328335</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>28.55993378419026</v>
+        <v>31.66072453877852</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>22.73956223359943</v>
+        <v>22.26308716583342</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28.71745007840202</v>
+        <v>27.24188580629671</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>23.25484214130603</v>
+        <v>26.21603964202922</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>20.14537880541877</v>
+        <v>27.59508886158095</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>28.45602822448586</v>
+        <v>30.81929358002933</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>28.46490860843006</v>
+        <v>31.70544510261495</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>22.61452790453408</v>
+        <v>22.009621651262</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>34.28740276267906</v>
+        <v>26.79188167401755</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>34.12306513337914</v>
+        <v>26.50534799034799</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>20.09543421849488</v>
+        <v>28.34134508748168</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>28.69823284502678</v>
+        <v>30.53540316960324</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>23.91953441838898</v>
+        <v>26.8643879816241</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>31.74694195463112</v>
+        <v>30.98493154014219</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>33.51353444447196</v>
+        <v>27.5018690765632</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>33.75119881150028</v>
+        <v>26.1662542241603</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>19.95932019402358</v>
+        <v>27.9988796337867</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>28.68060809814158</v>
+        <v>31.11743244940798</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>24.11665537178206</v>
+        <v>26.96598150003681</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>31.46470659543133</v>
+        <v>31.27646569722923</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>34.15737002190569</v>
+        <v>27.03015791298699</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>33.99654505462493</v>
+        <v>25.63357726261655</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>20.30192046346335</v>
+        <v>28.31187349236751</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>28.18251801554142</v>
+        <v>30.25456528939057</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>24.51805647132269</v>
+        <v>27.41225938924617</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>31.91116952950478</v>
+        <v>31.03495148921289</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>33.77699451092729</v>
+        <v>26.78858234633416</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>34.02043998895483</v>
+        <v>26.19577762557038</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>20.45773209563065</v>
+        <v>28.19747111872022</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>28.29278020018155</v>
+        <v>30.24592959850042</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>24.09002670990119</v>
+        <v>26.7975928549916</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>31.23692906987641</v>
+        <v>30.99353847049085</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>33.95590081017612</v>
+        <v>26.79393326575259</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>34.50101809943953</v>
+        <v>25.64131769422742</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>19.83293816867709</v>
+        <v>28.30705808814067</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>28.42773457792295</v>
+        <v>30.08812368210921</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>24.27943184917562</v>
+        <v>26.98085403139395</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>31.39825599773055</v>
+        <v>30.43501584310546</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>33.76266228809074</v>
+        <v>27.2003028575501</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>33.9787996787007</v>
+        <v>25.4501075999682</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>19.7419252255787</v>
+        <v>28.30092712452315</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>29.32113626650277</v>
+        <v>30.23638924892658</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>23.93511645105033</v>
+        <v>27.14167709149421</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>31.34401745625629</v>
+        <v>31.13623922015076</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>33.89782222602247</v>
+        <v>27.22224609338144</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>34.36790722144909</v>
+        <v>25.66130731639843</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>19.84339477177494</v>
+        <v>27.74612056122451</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>28.51227334448122</v>
+        <v>30.30787618571672</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>24.22061216619059</v>
+        <v>27.39432105373563</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>31.0552922919897</v>
+        <v>30.86530410430255</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>33.50690820456013</v>
+        <v>27.20932986187701</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>33.51566158705909</v>
+        <v>25.82157623022633</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>20.22744988112534</v>
+        <v>28.70258825405489</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>29.22135188795649</v>
+        <v>30.23797486249052</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>24.43750045461823</v>
+        <v>27.12734762572697</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>31.03120017379369</v>
+        <v>30.65903250118551</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>31.50238836791862</v>
+        <v>24.85048203176756</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>31.81414285832061</v>
+        <v>22.53177469330385</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>29.6891599603027</v>
+        <v>21.49727881884671</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>23.68906711325857</v>
+        <v>23.57956986501534</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>26.47500798836797</v>
+        <v>30.57355261231095</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>28.83237606906519</v>
+        <v>26.5991412599248</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>31.35003600513835</v>
+        <v>25.088010565681</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>31.9160154254459</v>
+        <v>22.28181971273294</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>29.98357918337848</v>
+        <v>21.73687495514663</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>24.15147915207519</v>
+        <v>23.61752523907687</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>26.19674276870598</v>
+        <v>30.79571391740229</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>28.76877339832027</v>
+        <v>26.3434144814795</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>31.70917376828989</v>
+        <v>24.5285810674513</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>31.23553279632959</v>
+        <v>22.84957967853174</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>29.43057271170418</v>
+        <v>22.04752838838318</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>23.86103926721848</v>
+        <v>23.89752195341204</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>26.40647045400232</v>
+        <v>30.8410242916107</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>28.87231150832085</v>
+        <v>26.06212299452766</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>31.59014375181805</v>
+        <v>24.83145977175429</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>31.35997175368312</v>
+        <v>22.06443526801909</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>29.9121498962737</v>
+        <v>22.44124562162252</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>23.61017261117837</v>
+        <v>23.1218503543567</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>25.70479520540017</v>
+        <v>30.3999637112921</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>28.20281802971987</v>
+        <v>26.27629884556568</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>31.68616914986581</v>
+        <v>24.58402590210929</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>31.27751792582732</v>
+        <v>22.32725077417401</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>29.62543359240186</v>
+        <v>21.8730061962383</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>23.71624201396563</v>
+        <v>23.41545247066238</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>25.82399737515556</v>
+        <v>30.73827655545743</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>28.31957314706055</v>
+        <v>26.29055474911515</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>31.92265363637207</v>
+        <v>24.97090538510626</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>32.24010956406255</v>
+        <v>22.69519246097</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>29.38008152815036</v>
+        <v>22.04622790207139</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>23.01173700119486</v>
+        <v>23.59771501881912</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>25.97179134443432</v>
+        <v>30.74484605673576</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>28.76634642011519</v>
+        <v>26.38626062884928</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>31.09843303468297</v>
+        <v>25.12437716369612</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>30.599455710758</v>
+        <v>22.1689031352374</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>29.47345795032039</v>
+        <v>21.84452538065771</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>23.34265573548663</v>
+        <v>23.09223967270563</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>26.48050425775492</v>
+        <v>30.90965811138855</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>28.86982497122615</v>
+        <v>26.89300021690915</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>31.74510098249836</v>
+        <v>24.89528671970104</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>31.75696785415209</v>
+        <v>22.61466073786054</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>29.59576734251451</v>
+        <v>21.68851118050813</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>23.80877373370624</v>
+        <v>23.21434679732148</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>26.03094873742024</v>
+        <v>30.64848135036062</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>28.59134430520947</v>
+        <v>25.84707617231707</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>31.94041686146799</v>
+        <v>30.55605321696325</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>29.34137456138508</v>
+        <v>28.93368763078428</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>24.92168243634886</v>
+        <v>24.62915330597514</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>30.82055235509403</v>
+        <v>26.87622373847067</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>33.4079931387621</v>
+        <v>29.17549358038486</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>30.26181573104521</v>
+        <v>25.65025381144795</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>32.24879226089242</v>
+        <v>30.20683715741288</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>29.32581279571836</v>
+        <v>28.75326071569278</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>24.32438949067328</v>
+        <v>24.35627867807953</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>30.88200890542878</v>
+        <v>26.18478266799378</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>33.91222569084454</v>
+        <v>29.3610576922954</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>30.29583849280444</v>
+        <v>26.35132404434718</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>32.39407587928497</v>
+        <v>30.41212599126302</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>29.14871059422359</v>
+        <v>29.21287146411851</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>24.89023201860716</v>
+        <v>24.15967496601459</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>30.53266080267829</v>
+        <v>26.38291038996358</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>33.75429149004402</v>
+        <v>29.61952408410542</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>30.27752222236737</v>
+        <v>26.16734103976462</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>32.83543016227583</v>
+        <v>30.35939658710665</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>29.75635010869831</v>
+        <v>29.31511831100753</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>24.18443655309791</v>
+        <v>23.89292985082979</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>30.84074892394237</v>
+        <v>25.99442579577928</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>33.1899832543601</v>
+        <v>29.22183167275787</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>30.04198401344856</v>
+        <v>25.59738623810595</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>32.24397324028452</v>
+        <v>30.42614522963896</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>29.10804956013337</v>
+        <v>29.03764800445114</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>24.35777106740808</v>
+        <v>24.54203812492083</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>30.44223554180371</v>
+        <v>26.55698492206513</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>33.53471982349205</v>
+        <v>29.31451784379512</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>29.46168928892019</v>
+        <v>25.71320601129113</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>32.29015100671702</v>
+        <v>30.3766078052967</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>28.79556053504204</v>
+        <v>29.65111099830203</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>24.30172163095502</v>
+        <v>24.85749046712502</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>30.41049940748991</v>
+        <v>26.3467921170775</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>33.30863337213201</v>
+        <v>29.27151350743383</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>29.63260214758923</v>
+        <v>26.04911403896736</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>31.74996877707522</v>
+        <v>30.63212055752771</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>29.20881085252847</v>
+        <v>29.72348063432543</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>24.74044778712073</v>
+        <v>24.27703895050821</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>31.07607515570463</v>
+        <v>25.96690755493239</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>33.59330327064729</v>
+        <v>29.82442243366828</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>29.29774000950494</v>
+        <v>26.24916263801092</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>32.11892829662923</v>
+        <v>30.31061247561276</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>29.32458594476672</v>
+        <v>29.32049884292457</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>24.27334278894775</v>
+        <v>24.22067167894018</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>30.3992451760515</v>
+        <v>26.44457137945727</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>34.11650266276052</v>
+        <v>29.84890979202334</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>30.08493953417796</v>
+        <v>25.53384532072636</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>26.64475613970544</v>
+        <v>27.17059745710916</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>30.18179312007887</v>
+        <v>25.60946264734929</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>31.01927137590491</v>
+        <v>26.46927292313549</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>31.17584070716758</v>
+        <v>28.69438786798113</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>31.74401294813208</v>
+        <v>34.63288190457732</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>34.52127146568227</v>
+        <v>30.00581751465992</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>27.90251226544275</v>
+        <v>27.16104953289262</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>29.58254098552658</v>
+        <v>25.28786637344177</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>31.72970030532386</v>
+        <v>26.37829136904806</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>30.97382776612824</v>
+        <v>28.66680853553855</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>31.36200703356615</v>
+        <v>34.35655437207589</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>34.62330058980275</v>
+        <v>29.51425019204286</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>27.70360356559018</v>
+        <v>26.78489348663505</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>29.91312979623033</v>
+        <v>25.51000256277827</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>31.34793725093935</v>
+        <v>26.56276277429776</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>30.40139560316358</v>
+        <v>29.03399349555936</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>31.95996709702643</v>
+        <v>34.25673494418972</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>34.54622259307232</v>
+        <v>30.25755760656848</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>27.36593120144549</v>
+        <v>26.44761622437177</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>29.79919858743531</v>
+        <v>25.92017193389993</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>31.44807177754928</v>
+        <v>26.42388828580743</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>30.72173322923711</v>
+        <v>29.08325235173962</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>31.10579388970011</v>
+        <v>33.72123838806414</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>34.43649178723095</v>
+        <v>29.6427287497111</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>27.08731291118906</v>
+        <v>26.9144344282885</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>30.09180771794482</v>
+        <v>25.9471389933965</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>31.14893077692459</v>
+        <v>26.50447891705464</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>31.33011623444187</v>
+        <v>28.41353600469596</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>31.02353050660958</v>
+        <v>33.95199263282678</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>34.43218007400142</v>
+        <v>30.03027587905633</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>27.5901602439873</v>
+        <v>27.25409812785542</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>30.32082980351497</v>
+        <v>25.88898128770616</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>31.62806546801916</v>
+        <v>27.00768642909581</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>30.77041721540098</v>
+        <v>28.87119763733479</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>31.13148217863998</v>
+        <v>33.48381120351291</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>34.01117400407948</v>
+        <v>30.5865478178396</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>27.82372603935761</v>
+        <v>26.41934513792456</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>29.93761380031195</v>
+        <v>25.20578973631931</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>31.55689112413804</v>
+        <v>26.53028951771763</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>30.3176188083776</v>
+        <v>28.35197826600643</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>31.37923489371287</v>
+        <v>33.83679058076239</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>34.25939281101892</v>
+        <v>30.05660552480695</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>27.5402357300516</v>
+        <v>26.98681317949345</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>29.53330474760273</v>
+        <v>25.77455965679514</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>31.56306134091226</v>
+        <v>26.2946471359922</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>30.71712059351419</v>
+        <v>29.16724171531122</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>31.55193412631351</v>
+        <v>34.02768227874152</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>34.48554648310837</v>
+        <v>30.29618851127431</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>29.15858299269645</v>
+        <v>24.91675693034816</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>28.67070464614751</v>
+        <v>28.68127252845425</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>26.57315175367366</v>
+        <v>25.82008541882155</v>
       </c>
     </row>
     <row r="293">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>29.72462402186491</v>
+        <v>26.21061122544728</v>
       </c>
     </row>
     <row r="294">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>30.58033590290009</v>
+        <v>33.25627102783059</v>
       </c>
     </row>
     <row r="295">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>21.65811509979481</v>
+        <v>25.16076934227204</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>29.29386661644348</v>
+        <v>24.52914777155417</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>28.54930303116323</v>
+        <v>28.4491282404271</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>26.2356143640987</v>
+        <v>25.7160560754088</v>
       </c>
     </row>
     <row r="299">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>29.45754785342478</v>
+        <v>26.67197517773903</v>
       </c>
     </row>
     <row r="300">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>31.29405157222848</v>
+        <v>32.94919943990102</v>
       </c>
     </row>
     <row r="301">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>21.93977479129002</v>
+        <v>24.91337034892678</v>
       </c>
     </row>
     <row r="302">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>28.97692574051912</v>
+        <v>24.8408485976476</v>
       </c>
     </row>
     <row r="303">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>29.36071076927728</v>
+        <v>28.66248408476537</v>
       </c>
     </row>
     <row r="304">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>25.95816821413532</v>
+        <v>25.97040310899364</v>
       </c>
     </row>
     <row r="305">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>29.77263806063981</v>
+        <v>26.60018991772794</v>
       </c>
     </row>
     <row r="306">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>30.62973109168695</v>
+        <v>33.16853693249467</v>
       </c>
     </row>
     <row r="307">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>21.76672364932406</v>
+        <v>25.12821452197577</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>28.88487790708302</v>
+        <v>24.18635959250795</v>
       </c>
     </row>
     <row r="309">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>28.98361381221733</v>
+        <v>28.19639033727793</v>
       </c>
     </row>
     <row r="310">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>26.22272207994123</v>
+        <v>25.92292975990029</v>
       </c>
     </row>
     <row r="311">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>29.1162470900519</v>
+        <v>25.90683846287381</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>30.68477032364282</v>
+        <v>32.78437800172186</v>
       </c>
     </row>
     <row r="313">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>22.00985183060646</v>
+        <v>25.24499343661963</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>29.42736511351247</v>
+        <v>24.81867257046623</v>
       </c>
     </row>
     <row r="315">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>28.23136871466429</v>
+        <v>28.31316801488556</v>
       </c>
     </row>
     <row r="316">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>26.31745020028302</v>
+        <v>26.18377008372106</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>29.46394097276065</v>
+        <v>26.4881921113273</v>
       </c>
     </row>
     <row r="318">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>30.51263819535131</v>
+        <v>32.65615187276654</v>
       </c>
     </row>
     <row r="319">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>22.0297097228649</v>
+        <v>25.51047798230415</v>
       </c>
     </row>
     <row r="320">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>29.22395750863224</v>
+        <v>25.00630532112408</v>
       </c>
     </row>
     <row r="321">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>28.52114999669924</v>
+        <v>28.06779612310145</v>
       </c>
     </row>
     <row r="322">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>26.44654639262599</v>
+        <v>25.57184427033931</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>29.51640768266355</v>
+        <v>26.18395084271341</v>
       </c>
     </row>
     <row r="324">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>30.49071147122902</v>
+        <v>32.88882452722667</v>
       </c>
     </row>
     <row r="325">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>21.60029033034041</v>
+        <v>25.14966012456469</v>
       </c>
     </row>
     <row r="326">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>28.83042859889686</v>
+        <v>24.70107021641936</v>
       </c>
     </row>
     <row r="327">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>28.09666976544536</v>
+        <v>28.40288884346018</v>
       </c>
     </row>
     <row r="328">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>26.21353911389393</v>
+        <v>25.73187838193907</v>
       </c>
     </row>
     <row r="329">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>28.87621959405397</v>
+        <v>26.78139558374229</v>
       </c>
     </row>
     <row r="330">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>31.11229844559902</v>
+        <v>32.80918317727731</v>
       </c>
     </row>
     <row r="331">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>22.19517419052199</v>
+        <v>25.00503160276917</v>
       </c>
     </row>
     <row r="332">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>28.72392435017658</v>
+        <v>24.71875180814104</v>
       </c>
     </row>
     <row r="333">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>28.83450859263097</v>
+        <v>28.47903732970146</v>
       </c>
     </row>
     <row r="334">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>26.185706576563</v>
+        <v>25.79501590448049</v>
       </c>
     </row>
     <row r="335">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>29.30833248782836</v>
+        <v>26.48042022090561</v>
       </c>
     </row>
     <row r="336">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>30.47253741415443</v>
+        <v>32.81095757386058</v>
       </c>
     </row>
     <row r="337">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>21.76520298408697</v>
+        <v>25.01835239382739</v>
       </c>
     </row>
     <row r="338">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>23.77062729008717</v>
+        <v>25.03070709361126</v>
       </c>
     </row>
     <row r="339">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>28.89563336957069</v>
+        <v>33.6689806542004</v>
       </c>
     </row>
     <row r="340">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>23.45658256053971</v>
+        <v>22.90372136849821</v>
       </c>
     </row>
     <row r="341">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>27.51216146148868</v>
+        <v>29.24890964184747</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>28.99623793860649</v>
+        <v>26.54936551110677</v>
       </c>
     </row>
     <row r="343">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>19.43133939793849</v>
+        <v>33.60072421844135</v>
       </c>
     </row>
     <row r="344">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>24.25343228011144</v>
+        <v>25.32097509378802</v>
       </c>
     </row>
     <row r="345">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>29.06398273638761</v>
+        <v>34.19652108148447</v>
       </c>
     </row>
     <row r="346">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>23.77949690433818</v>
+        <v>22.65161374676406</v>
       </c>
     </row>
     <row r="347">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>27.09329394986443</v>
+        <v>28.91492567644275</v>
       </c>
     </row>
     <row r="348">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>28.81188752553843</v>
+        <v>27.41796749042074</v>
       </c>
     </row>
     <row r="349">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>18.99452417509858</v>
+        <v>34.66708257237674</v>
       </c>
     </row>
     <row r="350">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>24.62774419881435</v>
+        <v>24.70672103180544</v>
       </c>
     </row>
     <row r="351">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>29.12855262599962</v>
+        <v>33.32831737462691</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>23.56955445817271</v>
+        <v>22.99432820227613</v>
       </c>
     </row>
     <row r="353">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>27.1935962749658</v>
+        <v>28.68256865016113</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>28.52805611967844</v>
+        <v>27.64023351764968</v>
       </c>
     </row>
     <row r="355">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>19.12287105559075</v>
+        <v>34.15969387923079</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>24.45251118925986</v>
+        <v>25.10310511866822</v>
       </c>
     </row>
     <row r="357">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>29.18741441097979</v>
+        <v>33.71879699437532</v>
       </c>
     </row>
     <row r="358">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>23.35107729430423</v>
+        <v>23.22499410588443</v>
       </c>
     </row>
     <row r="359">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>27.14979966602197</v>
+        <v>29.7402506417603</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>28.2986289289807</v>
+        <v>27.6305250428578</v>
       </c>
     </row>
     <row r="361">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>19.00334071378777</v>
+        <v>34.3010943216358</v>
       </c>
     </row>
     <row r="362">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>23.7632170753158</v>
+        <v>25.32222430822165</v>
       </c>
     </row>
     <row r="363">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>29.38015199249218</v>
+        <v>33.70322847193965</v>
       </c>
     </row>
     <row r="364">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>23.78987438534529</v>
+        <v>22.78785391420841</v>
       </c>
     </row>
     <row r="365">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>27.21446866396735</v>
+        <v>29.7239785947881</v>
       </c>
     </row>
     <row r="366">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>27.95180424295715</v>
+        <v>27.41000484557107</v>
       </c>
     </row>
     <row r="367">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>18.9257443001351</v>
+        <v>34.0608610785675</v>
       </c>
     </row>
     <row r="368">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>24.29000917741612</v>
+        <v>25.09786315970937</v>
       </c>
     </row>
     <row r="369">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>29.19174474612668</v>
+        <v>33.28948003291947</v>
       </c>
     </row>
     <row r="370">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>23.7279236498624</v>
+        <v>22.73729135987695</v>
       </c>
     </row>
     <row r="371">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>27.04639358419827</v>
+        <v>29.31608278654584</v>
       </c>
     </row>
     <row r="372">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>29.0890170783573</v>
+        <v>26.96209802646347</v>
       </c>
     </row>
     <row r="373">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>18.82668689332268</v>
+        <v>34.16379838297783</v>
       </c>
     </row>
     <row r="374">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>24.54600986429595</v>
+        <v>25.33642529913057</v>
       </c>
     </row>
     <row r="375">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>29.57692781307704</v>
+        <v>32.87383191828388</v>
       </c>
     </row>
     <row r="376">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>23.42235197082717</v>
+        <v>22.88388753955422</v>
       </c>
     </row>
     <row r="377">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>27.20897938517186</v>
+        <v>29.04281459340262</v>
       </c>
     </row>
     <row r="378">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>28.67182686986325</v>
+        <v>27.14973077181173</v>
       </c>
     </row>
     <row r="379">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>19.06456408215596</v>
+        <v>33.6904931761572</v>
       </c>
     </row>
     <row r="380">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>24.12799090111627</v>
+        <v>25.14244487230456</v>
       </c>
     </row>
     <row r="381">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>29.00829040657237</v>
+        <v>33.90480573003794</v>
       </c>
     </row>
     <row r="382">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>23.70454565117775</v>
+        <v>23.05946941191306</v>
       </c>
     </row>
     <row r="383">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>27.85473664400557</v>
+        <v>29.28270307402327</v>
       </c>
     </row>
     <row r="384">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>27.85454528482234</v>
+        <v>27.33768231968643</v>
       </c>
     </row>
     <row r="385">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>18.97014512744204</v>
+        <v>34.25787961235699</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.55976937021038</v>
+        <v>28.02690246928873</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.19391485692695</v>
+        <v>29.52864933636692</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.50411142857464</v>
+        <v>19.25469009362784</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.83195581255654</v>
+        <v>31.52727384074197</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.34655518807741</v>
+        <v>29.37764711891774</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.00142410743999</v>
+        <v>21.03409113050861</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.96511451945375</v>
+        <v>28.10599127726712</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31.22942729822399</v>
+        <v>29.63841142770631</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.27529891126438</v>
+        <v>19.52956986662128</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.29234847022125</v>
+        <v>31.64453492202614</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.13808391377904</v>
+        <v>29.31207010863239</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.09594887484221</v>
+        <v>21.03410401268011</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>27.0959009507392</v>
+        <v>28.5754226248624</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30.86297802804966</v>
+        <v>29.5096639262171</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29.98057436330386</v>
+        <v>19.3194997795138</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29.28406668117323</v>
+        <v>31.55464691028764</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.02487232170109</v>
+        <v>29.47781130440444</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.91214477264514</v>
+        <v>21.42343423279284</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.41645957588015</v>
+        <v>28.40030096762699</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>30.88200046194956</v>
+        <v>30.04057970220389</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30.18054868518402</v>
+        <v>19.6159844409461</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29.77265615819004</v>
+        <v>31.491997996675</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.26630438614874</v>
+        <v>29.64841458422849</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20.53970039707613</v>
+        <v>21.34146342277489</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.92314748106145</v>
+        <v>28.41138071422374</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.78050225524007</v>
+        <v>29.32740178144438</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30.4877456639553</v>
+        <v>19.58421475072393</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.97607434865328</v>
+        <v>31.49190941109028</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.28298061534533</v>
+        <v>29.41128977834309</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.10563860051205</v>
+        <v>21.15603995934542</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.13750021827272</v>
+        <v>28.53345285639657</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>30.99884885382235</v>
+        <v>29.1680129482205</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.42053452006191</v>
+        <v>19.57660444158692</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29.81673879041724</v>
+        <v>31.42943931245678</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.23141444258165</v>
+        <v>29.50673280794529</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>21.37982918826821</v>
+        <v>21.34118968602141</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.53783730613607</v>
+        <v>28.49128581130944</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31.66865875619099</v>
+        <v>29.17813887933007</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30.04491625977233</v>
+        <v>19.34715960720657</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29.5673613848153</v>
+        <v>30.96580967085238</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>28.14962044306536</v>
+        <v>29.61205858069214</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20.76648190113847</v>
+        <v>21.51566502367331</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>27.04125189036933</v>
+        <v>28.06258766696661</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30.90920129081247</v>
+        <v>29.54842101252539</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30.54302189484886</v>
+        <v>19.5131362110275</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>29.58438695315113</v>
+        <v>32.09802446887034</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.27936264515174</v>
+        <v>28.97531028942267</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20.85538062751549</v>
+        <v>21.16610134045887</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27.07412811556643</v>
+        <v>28.95854443171474</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>25.79226621969717</v>
+        <v>27.28752001713852</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27.58054206167661</v>
+        <v>29.62025533621535</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30.76394835233369</v>
+        <v>27.84276862618117</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32.08372004960465</v>
+        <v>29.18204814902807</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>22.37243627322901</v>
+        <v>22.76957778837673</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>27.18295761201992</v>
+        <v>29.47356447018847</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>26.42251190955269</v>
+        <v>27.44713679867888</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>27.88968668208256</v>
+        <v>29.84763523133746</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30.76420479142753</v>
+        <v>28.06173036789993</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>32.39599036937543</v>
+        <v>29.38271541105064</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.97134986153462</v>
+        <v>22.26926936354432</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>27.12759641311545</v>
+        <v>29.0910501909419</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>26.19241765616201</v>
+        <v>27.7840017168737</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>27.62280090456441</v>
+        <v>29.72193350964301</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>30.54720235765415</v>
+        <v>27.50631948826045</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32.07521418958203</v>
+        <v>29.20073877422704</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.30731590624156</v>
+        <v>22.55349840244784</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>27.12229407183639</v>
+        <v>29.38918130713581</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>26.75151325562631</v>
+        <v>27.81570322352529</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>27.97546380117557</v>
+        <v>30.14059886721881</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>30.7514567587041</v>
+        <v>27.93876034203124</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>31.90836050783833</v>
+        <v>29.51547931922042</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.13249422626382</v>
+        <v>22.92372933058775</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>27.34956941738156</v>
+        <v>28.85327770921523</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26.59049500467742</v>
+        <v>27.50279918168902</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27.70877669071917</v>
+        <v>29.16978620392342</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30.84797124675926</v>
+        <v>27.53150788733837</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>32.57190754673525</v>
+        <v>29.32742588385359</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>22.38419599878911</v>
+        <v>23.24302991567181</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>27.33144560758414</v>
+        <v>29.05552733292629</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>26.18911744028786</v>
+        <v>27.83809252729064</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>27.64807400833077</v>
+        <v>29.8831156615064</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>30.53263433476529</v>
+        <v>27.6786147898032</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>32.35997454469751</v>
+        <v>29.3207630658367</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>22.61373659716448</v>
+        <v>22.82108510437601</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>27.2110176800215</v>
+        <v>28.70698291006328</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>26.02242566852274</v>
+        <v>27.41960011169958</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>27.66236004408714</v>
+        <v>30.33094075963746</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>30.68063990328335</v>
+        <v>27.66534647220474</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>31.66072453877852</v>
+        <v>29.69153712911294</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>22.26308716583342</v>
+        <v>23.06756664768831</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>27.24188580629671</v>
+        <v>28.92221936237641</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>26.21603964202922</v>
+        <v>27.39209606225109</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>27.59508886158095</v>
+        <v>30.38627614031742</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>30.81929358002933</v>
+        <v>27.67255089959774</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>31.70544510261495</v>
+        <v>29.22784731694374</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>22.009621651262</v>
+        <v>22.88887858150546</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>26.79188167401755</v>
+        <v>30.11372817323361</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>26.50534799034799</v>
+        <v>27.33906892451274</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>28.34134508748168</v>
+        <v>25.58422579321016</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>30.53540316960324</v>
+        <v>26.79361342899624</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>26.8643879816241</v>
+        <v>33.1370204101817</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>30.98493154014219</v>
+        <v>26.20033835511396</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>27.5018690765632</v>
+        <v>30.68646612536697</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>26.1662542241603</v>
+        <v>27.45425250893936</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>27.9988796337867</v>
+        <v>25.71143122869889</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>31.11743244940798</v>
+        <v>26.36278082707205</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>26.96598150003681</v>
+        <v>33.53332471904791</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>31.27646569722923</v>
+        <v>25.83744420686522</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>27.03015791298699</v>
+        <v>30.73935116056556</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>25.63357726261655</v>
+        <v>27.70106565529818</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>28.31187349236751</v>
+        <v>25.20741001091291</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>30.25456528939057</v>
+        <v>26.60655349205711</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>27.41225938924617</v>
+        <v>33.79713126380078</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>31.03495148921289</v>
+        <v>25.79903794451682</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>26.78858234633416</v>
+        <v>31.06576617363366</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>26.19577762557038</v>
+        <v>27.46811350403212</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>28.19747111872022</v>
+        <v>25.46220690172656</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30.24592959850042</v>
+        <v>26.34847814802799</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>26.7975928549916</v>
+        <v>33.67015543335325</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30.99353847049085</v>
+        <v>26.81287522702105</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>26.79393326575259</v>
+        <v>30.47463726038879</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>25.64131769422742</v>
+        <v>27.63096109281351</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>28.30705808814067</v>
+        <v>25.5741802163793</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>30.08812368210921</v>
+        <v>26.88545568184887</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>26.98085403139395</v>
+        <v>32.98435888175984</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30.43501584310546</v>
+        <v>26.05742979068036</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>27.2003028575501</v>
+        <v>31.3059696552842</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>25.4501075999682</v>
+        <v>27.30967976745154</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>28.30092712452315</v>
+        <v>25.90200844782963</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>30.23638924892658</v>
+        <v>26.76010929766487</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>27.14167709149421</v>
+        <v>33.42858448108034</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>31.13623922015076</v>
+        <v>26.14399855111052</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.22224609338144</v>
+        <v>31.44835690811324</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>25.66130731639843</v>
+        <v>27.55212780871719</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>27.74612056122451</v>
+        <v>25.42903396812084</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>30.30787618571672</v>
+        <v>26.16483910441962</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>27.39432105373563</v>
+        <v>33.54024247935538</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>30.86530410430255</v>
+        <v>26.02060423163996</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>27.20932986187701</v>
+        <v>31.27667330142677</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>25.82157623022633</v>
+        <v>27.53464599338688</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>28.70258825405489</v>
+        <v>25.78744734519425</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>30.23797486249052</v>
+        <v>26.42687882336545</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>27.12734762572697</v>
+        <v>33.13512972378458</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>30.65903250118551</v>
+        <v>25.83036176310179</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>24.85048203176756</v>
+        <v>26.43209641797808</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>22.53177469330385</v>
+        <v>25.86555102842616</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>21.49727881884671</v>
+        <v>18.3459583182519</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>23.57956986501534</v>
+        <v>29.79743857975613</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.57355261231095</v>
+        <v>30.80146936286415</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>26.5991412599248</v>
+        <v>30.5025288331992</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>25.088010565681</v>
+        <v>26.06642802393182</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>22.28181971273294</v>
+        <v>26.35241115531299</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>21.73687495514663</v>
+        <v>18.13893877736601</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>23.61752523907687</v>
+        <v>29.57728105395752</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>30.79571391740229</v>
+        <v>31.37085749097491</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>26.3434144814795</v>
+        <v>29.9717811230677</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>24.5285810674513</v>
+        <v>27.03435916578976</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>22.84957967853174</v>
+        <v>26.26110236143241</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>22.04752838838318</v>
+        <v>18.32759513592249</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>23.89752195341204</v>
+        <v>29.11919792945356</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>30.8410242916107</v>
+        <v>30.58624625788905</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>26.06212299452766</v>
+        <v>30.00743299713834</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>24.83145977175429</v>
+        <v>26.24955281776244</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>22.06443526801909</v>
+        <v>26.37525041040178</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>22.44124562162252</v>
+        <v>18.46283119763287</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>23.1218503543567</v>
+        <v>29.25614238662131</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>30.3999637112921</v>
+        <v>30.90897918875258</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>26.27629884556568</v>
+        <v>30.04354549881173</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>24.58402590210929</v>
+        <v>26.74071215057142</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>22.32725077417401</v>
+        <v>26.40687034318487</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>21.8730061962383</v>
+        <v>18.61436550159693</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>23.41545247066238</v>
+        <v>29.33304548404387</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>30.73827655545743</v>
+        <v>30.8186260151568</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>26.29055474911515</v>
+        <v>29.62268606321781</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>24.97090538510626</v>
+        <v>26.77181334635784</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>22.69519246097</v>
+        <v>26.48539070895216</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>22.04622790207139</v>
+        <v>18.38162086137203</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>23.59771501881912</v>
+        <v>29.81102603675738</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>30.74484605673576</v>
+        <v>30.48525081237126</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>26.38626062884928</v>
+        <v>29.93060804183798</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>25.12437716369612</v>
+        <v>26.72043831688181</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>22.1689031352374</v>
+        <v>26.16886000341217</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>21.84452538065771</v>
+        <v>18.4802914056241</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>23.09223967270563</v>
+        <v>28.66303242615431</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>30.90965811138855</v>
+        <v>30.88355248863526</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>26.89300021690915</v>
+        <v>29.73041050202875</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>24.89528671970104</v>
+        <v>26.58793676224538</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>22.61466073786054</v>
+        <v>25.86650128270244</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>21.68851118050813</v>
+        <v>18.3439265208292</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>23.21434679732148</v>
+        <v>29.36271256291883</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>30.64848135036062</v>
+        <v>31.12636115143425</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>25.84707617231707</v>
+        <v>30.18135713770461</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>30.55605321696325</v>
+        <v>29.33664704365053</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>28.93368763078428</v>
+        <v>28.42726397527543</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>24.62915330597514</v>
+        <v>30.61058025738422</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>26.87622373847067</v>
+        <v>24.46770644909069</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>29.17549358038486</v>
+        <v>34.19795113766877</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>25.65025381144795</v>
+        <v>20.9796965560459</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>30.20683715741288</v>
+        <v>29.3827458297326</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>28.75326071569278</v>
+        <v>27.61725823759513</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>24.35627867807953</v>
+        <v>30.82562934902288</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>26.18478266799378</v>
+        <v>24.68592040010206</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>29.3610576922954</v>
+        <v>34.56402850584522</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>26.35132404434718</v>
+        <v>21.00518018863541</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>30.41212599126302</v>
+        <v>29.65074599670564</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>29.21287146411851</v>
+        <v>27.52572052867288</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>24.15967496601459</v>
+        <v>30.25627030943391</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>26.38291038996358</v>
+        <v>24.75594902132768</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>29.61952408410542</v>
+        <v>33.62298654733569</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>26.16734103976462</v>
+        <v>20.94011326246002</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>30.35939658710665</v>
+        <v>29.31260074862643</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>29.31511831100753</v>
+        <v>28.07089482030841</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>23.89292985082979</v>
+        <v>30.77725069300907</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>25.99442579577928</v>
+        <v>23.80969327789093</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>29.22183167275787</v>
+        <v>33.84869529518628</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>25.59738623810595</v>
+        <v>21.04037980233922</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>30.42614522963896</v>
+        <v>29.01036806448343</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>29.03764800445114</v>
+        <v>28.11793192388021</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>24.54203812492083</v>
+        <v>30.64722848068376</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>26.55698492206513</v>
+        <v>24.44882088656185</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>29.31451784379512</v>
+        <v>34.39022301280647</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>25.71320601129113</v>
+        <v>20.89352381307214</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>30.3766078052967</v>
+        <v>28.89147416625847</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>29.65111099830203</v>
+        <v>27.85998067207154</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>24.85749046712502</v>
+        <v>30.37848658018573</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>26.3467921170775</v>
+        <v>24.40272842975289</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>29.27151350743383</v>
+        <v>33.91876454126455</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>26.04911403896736</v>
+        <v>21.00560378466258</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>30.63212055752771</v>
+        <v>29.67888606756471</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>29.72348063432543</v>
+        <v>27.8686775212863</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>24.27703895050821</v>
+        <v>31.01821393934398</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>25.96690755493239</v>
+        <v>24.17090728805646</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>29.82442243366828</v>
+        <v>34.75082461988752</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>26.24916263801092</v>
+        <v>20.78205515058013</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>30.31061247561276</v>
+        <v>28.81783618800371</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>29.32049884292457</v>
+        <v>28.02452360944054</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>24.22067167894018</v>
+        <v>30.18200833780461</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>26.44457137945727</v>
+        <v>24.29766018545764</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>29.84890979202334</v>
+        <v>34.22711999396716</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>25.53384532072636</v>
+        <v>20.77355492529803</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>27.17059745710916</v>
+        <v>27.69549436659453</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>25.60946264734929</v>
+        <v>27.00306059738566</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>26.46927292313549</v>
+        <v>21.92188395201839</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>28.69438786798113</v>
+        <v>30.22813228434276</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>34.63288190457732</v>
+        <v>27.96465457200469</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>30.00581751465992</v>
+        <v>30.37230640707619</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>27.16104953289262</v>
+        <v>28.06161607141452</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>25.28786637344177</v>
+        <v>26.37254480673009</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>26.37829136904806</v>
+        <v>21.48630261199635</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>28.66680853553855</v>
+        <v>29.86634827071052</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>34.35655437207589</v>
+        <v>28.4065554848563</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>29.51425019204286</v>
+        <v>30.02669172511998</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>26.78489348663505</v>
+        <v>27.89499109775855</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>25.51000256277827</v>
+        <v>26.66508131193297</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>26.56276277429776</v>
+        <v>21.52961271744196</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>29.03399349555936</v>
+        <v>30.45856793143744</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>34.25673494418972</v>
+        <v>28.25583366651533</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>30.25755760656848</v>
+        <v>30.38548742590624</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>26.44761622437177</v>
+        <v>27.97322438998012</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>25.92017193389993</v>
+        <v>26.31101169677933</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>26.42388828580743</v>
+        <v>21.54193872312522</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>29.08325235173962</v>
+        <v>29.77109110884435</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>33.72123838806414</v>
+        <v>27.58048462053506</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>29.6427287497111</v>
+        <v>29.50334832291697</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>26.9144344282885</v>
+        <v>28.21035341336024</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>25.9471389933965</v>
+        <v>26.2691836476769</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>26.50447891705464</v>
+        <v>21.957884528304</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>28.41353600469596</v>
+        <v>30.07761258331605</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>33.95199263282678</v>
+        <v>28.40702883873739</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>30.03027587905633</v>
+        <v>29.98784742154112</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>27.25409812785542</v>
+        <v>27.7382138046033</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>25.88898128770616</v>
+        <v>26.58276819573032</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>27.00768642909581</v>
+        <v>21.79050724751803</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>28.87119763733479</v>
+        <v>29.51179448529111</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>33.48381120351291</v>
+        <v>28.43776195577552</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>30.5865478178396</v>
+        <v>29.99406543957371</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>26.41934513792456</v>
+        <v>27.94551818216612</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>25.20578973631931</v>
+        <v>26.45242423397816</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>26.53028951771763</v>
+        <v>21.3979433284949</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>28.35197826600643</v>
+        <v>30.15306770913</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>33.83679058076239</v>
+        <v>28.55853473700517</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>30.05660552480695</v>
+        <v>29.90596986850489</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>26.98681317949345</v>
+        <v>28.15362943816656</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>25.77455965679514</v>
+        <v>26.12141325493272</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>26.2946471359922</v>
+        <v>21.35797047600099</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>29.16724171531122</v>
+        <v>29.55068908734235</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>34.02768227874152</v>
+        <v>28.41617696771539</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>30.29618851127431</v>
+        <v>29.48125222182376</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>24.91675693034816</v>
+        <v>33.17946765510813</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>28.68127252845425</v>
+        <v>27.76605875876434</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>25.82008541882155</v>
+        <v>24.57911195620843</v>
       </c>
     </row>
     <row r="293">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>26.21061122544728</v>
+        <v>31.20653628400258</v>
       </c>
     </row>
     <row r="294">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>33.25627102783059</v>
+        <v>28.06266205665846</v>
       </c>
     </row>
     <row r="295">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>25.16076934227204</v>
+        <v>27.97540545039952</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>24.52914777155417</v>
+        <v>33.84341717593075</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>28.4491282404271</v>
+        <v>28.00458364391239</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>25.7160560754088</v>
+        <v>24.0405647676623</v>
       </c>
     </row>
     <row r="299">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>26.67197517773903</v>
+        <v>31.32725856007287</v>
       </c>
     </row>
     <row r="300">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>32.94919943990102</v>
+        <v>27.80750720203176</v>
       </c>
     </row>
     <row r="301">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>24.91337034892678</v>
+        <v>27.73137065706267</v>
       </c>
     </row>
     <row r="302">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>24.8408485976476</v>
+        <v>33.26428796948102</v>
       </c>
     </row>
     <row r="303">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>28.66248408476537</v>
+        <v>27.98761119558209</v>
       </c>
     </row>
     <row r="304">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>25.97040310899364</v>
+        <v>24.41912809958805</v>
       </c>
     </row>
     <row r="305">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>26.60018991772794</v>
+        <v>31.65357019373381</v>
       </c>
     </row>
     <row r="306">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>33.16853693249467</v>
+        <v>27.37002651439098</v>
       </c>
     </row>
     <row r="307">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>25.12821452197577</v>
+        <v>27.77643469122015</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>24.18635959250795</v>
+        <v>33.54085703642179</v>
       </c>
     </row>
     <row r="309">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>28.19639033727793</v>
+        <v>27.95731612173426</v>
       </c>
     </row>
     <row r="310">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>25.92292975990029</v>
+        <v>24.10529591085661</v>
       </c>
     </row>
     <row r="311">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>25.90683846287381</v>
+        <v>30.96136972589564</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>32.78437800172186</v>
+        <v>27.64457152816048</v>
       </c>
     </row>
     <row r="313">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>25.24499343661963</v>
+        <v>27.76613930184232</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>24.81867257046623</v>
+        <v>33.57046999349766</v>
       </c>
     </row>
     <row r="315">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>28.31316801488556</v>
+        <v>28.02512952648664</v>
       </c>
     </row>
     <row r="316">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>26.18377008372106</v>
+        <v>24.49865959276603</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>26.4881921113273</v>
+        <v>31.29919882773843</v>
       </c>
     </row>
     <row r="318">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>32.65615187276654</v>
+        <v>27.77775217200644</v>
       </c>
     </row>
     <row r="319">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>25.51047798230415</v>
+        <v>27.52315849148129</v>
       </c>
     </row>
     <row r="320">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>25.00630532112408</v>
+        <v>33.85956880295198</v>
       </c>
     </row>
     <row r="321">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>28.06779612310145</v>
+        <v>28.18544445620648</v>
       </c>
     </row>
     <row r="322">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>25.57184427033931</v>
+        <v>24.29111752728461</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>26.18395084271341</v>
+        <v>31.36816047942404</v>
       </c>
     </row>
     <row r="324">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>32.88882452722667</v>
+        <v>27.8826303934463</v>
       </c>
     </row>
     <row r="325">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>25.14966012456469</v>
+        <v>27.67242228038597</v>
       </c>
     </row>
     <row r="326">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>24.70107021641936</v>
+        <v>33.67384339814065</v>
       </c>
     </row>
     <row r="327">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>28.40288884346018</v>
+        <v>28.32407032984672</v>
       </c>
     </row>
     <row r="328">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>25.73187838193907</v>
+        <v>24.7035309368722</v>
       </c>
     </row>
     <row r="329">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>26.78139558374229</v>
+        <v>31.45546168696109</v>
       </c>
     </row>
     <row r="330">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>32.80918317727731</v>
+        <v>28.04477515564096</v>
       </c>
     </row>
     <row r="331">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>25.00503160276917</v>
+        <v>27.84362807957203</v>
       </c>
     </row>
     <row r="332">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>24.71875180814104</v>
+        <v>33.01930089337686</v>
       </c>
     </row>
     <row r="333">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>28.47903732970146</v>
+        <v>28.13592841460885</v>
       </c>
     </row>
     <row r="334">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>25.79501590448049</v>
+        <v>24.59069050413607</v>
       </c>
     </row>
     <row r="335">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>26.48042022090561</v>
+        <v>31.64144848742452</v>
       </c>
     </row>
     <row r="336">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>32.81095757386058</v>
+        <v>27.35457641501443</v>
       </c>
     </row>
     <row r="337">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>25.01835239382739</v>
+        <v>27.37402386209934</v>
       </c>
     </row>
     <row r="338">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>25.03070709361126</v>
+        <v>31.51048184288915</v>
       </c>
     </row>
     <row r="339">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>33.6689806542004</v>
+        <v>27.11201325431221</v>
       </c>
     </row>
     <row r="340">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>22.90372136849821</v>
+        <v>29.69549013239058</v>
       </c>
     </row>
     <row r="341">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>29.24890964184747</v>
+        <v>24.04402035424124</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>26.54936551110677</v>
+        <v>29.21428010374946</v>
       </c>
     </row>
     <row r="343">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>33.60072421844135</v>
+        <v>29.38631578956175</v>
       </c>
     </row>
     <row r="344">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>25.32097509378802</v>
+        <v>31.64181026861563</v>
       </c>
     </row>
     <row r="345">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>34.19652108148447</v>
+        <v>27.01462784062903</v>
       </c>
     </row>
     <row r="346">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>22.65161374676406</v>
+        <v>29.33340855542288</v>
       </c>
     </row>
     <row r="347">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>28.91492567644275</v>
+        <v>24.09827052784859</v>
       </c>
     </row>
     <row r="348">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>27.41796749042074</v>
+        <v>29.53125238084446</v>
       </c>
     </row>
     <row r="349">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>34.66708257237674</v>
+        <v>29.49453204093082</v>
       </c>
     </row>
     <row r="350">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>24.70672103180544</v>
+        <v>31.86620729509612</v>
       </c>
     </row>
     <row r="351">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>33.32831737462691</v>
+        <v>26.64956369798982</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>22.99432820227613</v>
+        <v>29.50429902950926</v>
       </c>
     </row>
     <row r="353">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>28.68256865016113</v>
+        <v>24.09123422841502</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>27.64023351764968</v>
+        <v>29.84414053962257</v>
       </c>
     </row>
     <row r="355">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>34.15969387923079</v>
+        <v>29.43778376761604</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>25.10310511866822</v>
+        <v>31.80536666178724</v>
       </c>
     </row>
     <row r="357">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>33.71879699437532</v>
+        <v>27.12675400997624</v>
       </c>
     </row>
     <row r="358">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>23.22499410588443</v>
+        <v>29.51192484268571</v>
       </c>
     </row>
     <row r="359">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>29.7402506417603</v>
+        <v>23.66229489123959</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>27.6305250428578</v>
+        <v>29.70745054049908</v>
       </c>
     </row>
     <row r="361">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>34.3010943216358</v>
+        <v>28.4987953424984</v>
       </c>
     </row>
     <row r="362">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>25.32222430822165</v>
+        <v>32.12619692026055</v>
       </c>
     </row>
     <row r="363">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>33.70322847193965</v>
+        <v>27.30234673850719</v>
       </c>
     </row>
     <row r="364">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>22.78785391420841</v>
+        <v>29.47539129484338</v>
       </c>
     </row>
     <row r="365">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>29.7239785947881</v>
+        <v>24.12397146388378</v>
       </c>
     </row>
     <row r="366">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>27.41000484557107</v>
+        <v>29.89303665971735</v>
       </c>
     </row>
     <row r="367">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>34.0608610785675</v>
+        <v>29.11499370566098</v>
       </c>
     </row>
     <row r="368">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>25.09786315970937</v>
+        <v>31.21309784439669</v>
       </c>
     </row>
     <row r="369">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>33.28948003291947</v>
+        <v>26.78916334413007</v>
       </c>
     </row>
     <row r="370">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>22.73729135987695</v>
+        <v>30.34604498568811</v>
       </c>
     </row>
     <row r="371">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>29.31608278654584</v>
+        <v>23.8930992592082</v>
       </c>
     </row>
     <row r="372">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>26.96209802646347</v>
+        <v>29.31521545390397</v>
       </c>
     </row>
     <row r="373">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>34.16379838297783</v>
+        <v>29.55478419437644</v>
       </c>
     </row>
     <row r="374">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>25.33642529913057</v>
+        <v>31.65893374245231</v>
       </c>
     </row>
     <row r="375">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>32.87383191828388</v>
+        <v>27.1544621458586</v>
       </c>
     </row>
     <row r="376">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>22.88388753955422</v>
+        <v>29.74516784298643</v>
       </c>
     </row>
     <row r="377">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>29.04281459340262</v>
+        <v>23.71233985905886</v>
       </c>
     </row>
     <row r="378">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>27.14973077181173</v>
+        <v>30.05600803974308</v>
       </c>
     </row>
     <row r="379">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>33.6904931761572</v>
+        <v>28.77036138814645</v>
       </c>
     </row>
     <row r="380">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>25.14244487230456</v>
+        <v>31.72282794252184</v>
       </c>
     </row>
     <row r="381">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>33.90480573003794</v>
+        <v>27.0994628714455</v>
       </c>
     </row>
     <row r="382">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>23.05946941191306</v>
+        <v>29.93694828499462</v>
       </c>
     </row>
     <row r="383">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>29.28270307402327</v>
+        <v>24.37849404272714</v>
       </c>
     </row>
     <row r="384">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>27.33768231968643</v>
+        <v>29.62048259901244</v>
       </c>
     </row>
     <row r="385">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>34.25787961235699</v>
+        <v>29.0144681155782</v>
       </c>
     </row>
   </sheetData>

--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios188.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.02690246928873</v>
+        <v>30.0853187380475</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.52864933636692</v>
+        <v>23.12369601522129</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.25469009362784</v>
+        <v>27.26532160975045</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.52727384074197</v>
+        <v>26.85861460724102</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.37764711891774</v>
+        <v>27.5733656442835</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.03409113050861</v>
+        <v>28.26613509053244</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.10599127726712</v>
+        <v>29.89369070365238</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>29.63841142770631</v>
+        <v>22.87845444676072</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.52956986662128</v>
+        <v>27.21995466117444</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31.64453492202614</v>
+        <v>27.03054725563269</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>29.31207010863239</v>
+        <v>28.49678574744939</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.03410401268011</v>
+        <v>28.43509237705367</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.5754226248624</v>
+        <v>30.07374912477554</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>29.5096639262171</v>
+        <v>23.04631774045898</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.3194997795138</v>
+        <v>26.74079508798118</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31.55464691028764</v>
+        <v>26.91463161036991</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.47781130440444</v>
+        <v>27.98607992743867</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21.42343423279284</v>
+        <v>29.08474204068694</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.40030096762699</v>
+        <v>29.93879149633678</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>30.04057970220389</v>
+        <v>23.133034898786</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.6159844409461</v>
+        <v>27.25446368892001</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31.491997996675</v>
+        <v>26.60714080600722</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.64841458422849</v>
+        <v>28.28887278626872</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21.34146342277489</v>
+        <v>28.59897775964668</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.41138071422374</v>
+        <v>30.23377488268549</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.32740178144438</v>
+        <v>22.85375110243023</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19.58421475072393</v>
+        <v>27.64638430427586</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31.49190941109028</v>
+        <v>26.54436650136627</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.41128977834309</v>
+        <v>28.13337343288733</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.15603995934542</v>
+        <v>29.00731013014455</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28.53345285639657</v>
+        <v>29.69936687992453</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>29.1680129482205</v>
+        <v>22.93287955853662</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19.57660444158692</v>
+        <v>27.29109635655066</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>31.42943931245678</v>
+        <v>26.78622505916637</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29.50673280794529</v>
+        <v>27.53552531550904</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>21.34118968602141</v>
+        <v>28.40499949542222</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>28.49128581130944</v>
+        <v>29.6778391801997</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>29.17813887933007</v>
+        <v>23.1727144963326</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19.34715960720657</v>
+        <v>27.01325632417877</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30.96580967085238</v>
+        <v>27.33903938453419</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>29.61205858069214</v>
+        <v>27.75016405294309</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>21.51566502367331</v>
+        <v>28.29411863393847</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>28.06258766696661</v>
+        <v>30.24051967523399</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>29.54842101252539</v>
+        <v>22.77960732642177</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>19.5131362110275</v>
+        <v>27.32594199225768</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>32.09802446887034</v>
+        <v>27.27367557567923</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.97531028942267</v>
+        <v>27.51963325171168</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>21.16610134045887</v>
+        <v>28.43794683967966</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>28.95854443171474</v>
+        <v>32.07303485763677</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27.28752001713852</v>
+        <v>30.84688142834338</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>29.62025533621535</v>
+        <v>22.44592923236874</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>27.84276862618117</v>
+        <v>26.77590993869613</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>29.18204814902807</v>
+        <v>31.15555976851631</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>22.76957778837673</v>
+        <v>29.89314116689913</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29.47356447018847</v>
+        <v>32.07003102410232</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.44713679867888</v>
+        <v>30.71362376141913</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>29.84763523133746</v>
+        <v>22.57250208966166</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>28.06173036789993</v>
+        <v>27.1972255427317</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>29.38271541105064</v>
+        <v>31.08462456199494</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>22.26926936354432</v>
+        <v>29.59171622733891</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>29.0910501909419</v>
+        <v>32.58675798974242</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>27.7840017168737</v>
+        <v>30.75261314439343</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>29.72193350964301</v>
+        <v>22.45630349820185</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>27.50631948826045</v>
+        <v>27.31235595200049</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>29.20073877422704</v>
+        <v>30.69169950130432</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>22.55349840244784</v>
+        <v>30.03921361819298</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>29.38918130713581</v>
+        <v>32.36053216632335</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>27.81570322352529</v>
+        <v>30.35639330082552</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30.14059886721881</v>
+        <v>22.9459986499997</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>27.93876034203124</v>
+        <v>27.24621017196735</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>29.51547931922042</v>
+        <v>31.24857789629164</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>22.92372933058775</v>
+        <v>30.36995805017136</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.85327770921523</v>
+        <v>31.91139920571509</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>27.50279918168902</v>
+        <v>30.37688390136735</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>29.16978620392342</v>
+        <v>22.52489125549262</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27.53150788733837</v>
+        <v>26.9128417096471</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>29.32742588385359</v>
+        <v>30.96989355208163</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>23.24302991567181</v>
+        <v>29.90630506594851</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>29.05552733292629</v>
+        <v>32.07841172142162</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>27.83809252729064</v>
+        <v>30.86076514406685</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>29.8831156615064</v>
+        <v>22.73000660611551</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.6786147898032</v>
+        <v>27.52861026891005</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>29.3207630658367</v>
+        <v>30.91176311031762</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>22.82108510437601</v>
+        <v>30.61536224233168</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>28.70698291006328</v>
+        <v>32.19004896545693</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>27.41960011169958</v>
+        <v>30.34522911157405</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>30.33094075963746</v>
+        <v>22.48366936818038</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.66534647220474</v>
+        <v>27.2651204035143</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>29.69153712911294</v>
+        <v>30.92453070714119</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>23.06756664768831</v>
+        <v>30.01743117264935</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28.92221936237641</v>
+        <v>32.14128685154849</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>27.39209606225109</v>
+        <v>30.58529316266471</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>30.38627614031742</v>
+        <v>22.53460041367748</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>27.67255089959774</v>
+        <v>26.72316359096767</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>29.22784731694374</v>
+        <v>30.85539838633474</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>22.88887858150546</v>
+        <v>30.05987245345765</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>30.11372817323361</v>
+        <v>27.66950683805296</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>27.33906892451274</v>
+        <v>27.13782391973364</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>25.58422579321016</v>
+        <v>21.7228483936089</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>26.79361342899624</v>
+        <v>24.74560458124206</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>33.1370204101817</v>
+        <v>32.1508755266154</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>26.20033835511396</v>
+        <v>31.33743567651315</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>30.68646612536697</v>
+        <v>27.62646636716737</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>27.45425250893936</v>
+        <v>27.1660648574326</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>25.71143122869889</v>
+        <v>21.76288084093663</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>26.36278082707205</v>
+        <v>24.78885832333376</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>33.53332471904791</v>
+        <v>32.78889305319687</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>25.83744420686522</v>
+        <v>31.61906377743652</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>30.73935116056556</v>
+        <v>27.23001475995352</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>27.70106565529818</v>
+        <v>27.22243909200669</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>25.20741001091291</v>
+        <v>21.79698051122132</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>26.60655349205711</v>
+        <v>24.77727288241</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>33.79713126380078</v>
+        <v>32.60464645942106</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>25.79903794451682</v>
+        <v>32.49483021700793</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>31.06576617363366</v>
+        <v>27.7680198336144</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>27.46811350403212</v>
+        <v>27.79221006186055</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>25.46220690172656</v>
+        <v>21.8921716847523</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>26.34847814802799</v>
+        <v>24.8111934441087</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>33.67015543335325</v>
+        <v>32.33531176172219</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>26.81287522702105</v>
+        <v>31.52681254180862</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>30.47463726038879</v>
+        <v>27.39701461809451</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27.63096109281351</v>
+        <v>27.41507674545921</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>25.5741802163793</v>
+        <v>21.58004109099569</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>26.88545568184887</v>
+        <v>24.67080393674179</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>32.98435888175984</v>
+        <v>33.1883966328481</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>26.05742979068036</v>
+        <v>30.70508122922451</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>31.3059696552842</v>
+        <v>27.79987385755037</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27.30967976745154</v>
+        <v>27.03697804640046</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>25.90200844782963</v>
+        <v>21.5829537906816</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>26.76010929766487</v>
+        <v>24.91905454203809</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>33.42858448108034</v>
+        <v>32.45842834817261</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>26.14399855111052</v>
+        <v>30.95211692543657</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>31.44835690811324</v>
+        <v>27.41289653274493</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>27.55212780871719</v>
+        <v>27.66690937920993</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>25.42903396812084</v>
+        <v>21.52691145292214</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>26.16483910441962</v>
+        <v>24.70397984009355</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>33.54024247935538</v>
+        <v>32.45235986805462</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>26.02060423163996</v>
+        <v>31.0854546885606</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>31.27667330142677</v>
+        <v>28.20234613567843</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.53464599338688</v>
+        <v>27.65435679439516</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>25.78744734519425</v>
+        <v>21.24613548561328</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>26.42687882336545</v>
+        <v>24.69658359988992</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>33.13512972378458</v>
+        <v>32.22290997000602</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>25.83036176310179</v>
+        <v>31.55605684267644</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>26.43209641797808</v>
+        <v>28.5629946491987</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>25.86555102842616</v>
+        <v>30.77454194026616</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>18.3459583182519</v>
+        <v>27.54879943231923</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>29.79743857975613</v>
+        <v>26.42043769967777</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30.80146936286415</v>
+        <v>30.71108443900398</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>30.5025288331992</v>
+        <v>31.89130775774083</v>
       </c>
     </row>
     <row r="152">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>26.06642802393182</v>
+        <v>28.65442833239878</v>
       </c>
     </row>
     <row r="153">
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>26.35241115531299</v>
+        <v>30.60860208239184</v>
       </c>
     </row>
     <row r="154">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>18.13893877736601</v>
+        <v>27.89429822245935</v>
       </c>
     </row>
     <row r="155">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>29.57728105395752</v>
+        <v>26.29974423851887</v>
       </c>
     </row>
     <row r="156">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>31.37085749097491</v>
+        <v>30.69225129262015</v>
       </c>
     </row>
     <row r="157">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>29.9717811230677</v>
+        <v>32.2920432197155</v>
       </c>
     </row>
     <row r="158">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>27.03435916578976</v>
+        <v>29.40216425950368</v>
       </c>
     </row>
     <row r="159">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>26.26110236143241</v>
+        <v>31.12799354698901</v>
       </c>
     </row>
     <row r="160">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>18.32759513592249</v>
+        <v>26.99391540885022</v>
       </c>
     </row>
     <row r="161">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>29.11919792945356</v>
+        <v>26.06682603775835</v>
       </c>
     </row>
     <row r="162">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>30.58624625788905</v>
+        <v>31.4779958449378</v>
       </c>
     </row>
     <row r="163">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>30.00743299713834</v>
+        <v>31.77190010906777</v>
       </c>
     </row>
     <row r="164">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>26.24955281776244</v>
+        <v>28.918951456341</v>
       </c>
     </row>
     <row r="165">
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>26.37525041040178</v>
+        <v>31.04855603023831</v>
       </c>
     </row>
     <row r="166">
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>18.46283119763287</v>
+        <v>27.15630532847723</v>
       </c>
     </row>
     <row r="167">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>29.25614238662131</v>
+        <v>26.17807281493502</v>
       </c>
     </row>
     <row r="168">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>30.90897918875258</v>
+        <v>30.07666522131515</v>
       </c>
     </row>
     <row r="169">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>30.04354549881173</v>
+        <v>31.67055554209665</v>
       </c>
     </row>
     <row r="170">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>26.74071215057142</v>
+        <v>28.7184533199484</v>
       </c>
     </row>
     <row r="171">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>26.40687034318487</v>
+        <v>30.42545146191644</v>
       </c>
     </row>
     <row r="172">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>18.61436550159693</v>
+        <v>27.85783064738067</v>
       </c>
     </row>
     <row r="173">
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>29.33304548404387</v>
+        <v>25.81905825001109</v>
       </c>
     </row>
     <row r="174">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>30.8186260151568</v>
+        <v>30.94740256620453</v>
       </c>
     </row>
     <row r="175">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>29.62268606321781</v>
+        <v>32.04017742706655</v>
       </c>
     </row>
     <row r="176">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>26.77181334635784</v>
+        <v>29.2061300995677</v>
       </c>
     </row>
     <row r="177">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>26.48539070895216</v>
+        <v>30.36750453441212</v>
       </c>
     </row>
     <row r="178">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>18.38162086137203</v>
+        <v>27.72920810796261</v>
       </c>
     </row>
     <row r="179">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>29.81102603675738</v>
+        <v>26.19634510079635</v>
       </c>
     </row>
     <row r="180">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>30.48525081237126</v>
+        <v>30.77909283381314</v>
       </c>
     </row>
     <row r="181">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>29.93060804183798</v>
+        <v>32.14620806212114</v>
       </c>
     </row>
     <row r="182">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>26.72043831688181</v>
+        <v>28.84848226405982</v>
       </c>
     </row>
     <row r="183">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>26.16886000341217</v>
+        <v>30.62496594179443</v>
       </c>
     </row>
     <row r="184">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>18.4802914056241</v>
+        <v>27.42951351477685</v>
       </c>
     </row>
     <row r="185">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>28.66303242615431</v>
+        <v>26.09273693554986</v>
       </c>
     </row>
     <row r="186">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>30.88355248863526</v>
+        <v>31.1194727601923</v>
       </c>
     </row>
     <row r="187">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>29.73041050202875</v>
+        <v>32.21021345097125</v>
       </c>
     </row>
     <row r="188">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>26.58793676224538</v>
+        <v>29.24780345545017</v>
       </c>
     </row>
     <row r="189">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>25.86650128270244</v>
+        <v>30.42852249433754</v>
       </c>
     </row>
     <row r="190">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>18.3439265208292</v>
+        <v>27.99505306182169</v>
       </c>
     </row>
     <row r="191">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>29.36271256291883</v>
+        <v>25.68234135450083</v>
       </c>
     </row>
     <row r="192">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>31.12636115143425</v>
+        <v>31.03700565402474</v>
       </c>
     </row>
     <row r="193">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>30.18135713770461</v>
+        <v>32.18659436457719</v>
       </c>
     </row>
     <row r="194">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>29.33664704365053</v>
+        <v>28.97730019028065</v>
       </c>
     </row>
     <row r="195">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>28.42726397527543</v>
+        <v>32.17936589084081</v>
       </c>
     </row>
     <row r="196">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>30.61058025738422</v>
+        <v>15.7501461715677</v>
       </c>
     </row>
     <row r="197">
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>24.46770644909069</v>
+        <v>30.1519411868662</v>
       </c>
     </row>
     <row r="198">
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>34.19795113766877</v>
+        <v>30.0827927034048</v>
       </c>
     </row>
     <row r="199">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>20.9796965560459</v>
+        <v>25.04486042480135</v>
       </c>
     </row>
     <row r="200">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>29.3827458297326</v>
+        <v>28.99926805443888</v>
       </c>
     </row>
     <row r="201">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>27.61725823759513</v>
+        <v>32.15663116474247</v>
       </c>
     </row>
     <row r="202">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>30.82562934902288</v>
+        <v>15.92497788925971</v>
       </c>
     </row>
     <row r="203">
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>24.68592040010206</v>
+        <v>30.39444284497853</v>
       </c>
     </row>
     <row r="204">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>34.56402850584522</v>
+        <v>30.507122558296</v>
       </c>
     </row>
     <row r="205">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>21.00518018863541</v>
+        <v>24.99023254966304</v>
       </c>
     </row>
     <row r="206">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>29.65074599670564</v>
+        <v>28.65655722203655</v>
       </c>
     </row>
     <row r="207">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>27.52572052867288</v>
+        <v>32.19961000112582</v>
       </c>
     </row>
     <row r="208">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>30.25627030943391</v>
+        <v>15.90093939961181</v>
       </c>
     </row>
     <row r="209">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>24.75594902132768</v>
+        <v>30.48627730236517</v>
       </c>
     </row>
     <row r="210">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>33.62298654733569</v>
+        <v>30.25481614385098</v>
       </c>
     </row>
     <row r="211">
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>20.94011326246002</v>
+        <v>24.86300826459261</v>
       </c>
     </row>
     <row r="212">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>29.31260074862643</v>
+        <v>29.26529986985653</v>
       </c>
     </row>
     <row r="213">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>28.07089482030841</v>
+        <v>32.1894454916311</v>
       </c>
     </row>
     <row r="214">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>30.77725069300907</v>
+        <v>15.86934244140877</v>
       </c>
     </row>
     <row r="215">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>23.80969327789093</v>
+        <v>30.24005995544189</v>
       </c>
     </row>
     <row r="216">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>33.84869529518628</v>
+        <v>30.1952683884298</v>
       </c>
     </row>
     <row r="217">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>21.04037980233922</v>
+        <v>25.10674016284441</v>
       </c>
     </row>
     <row r="218">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>29.01036806448343</v>
+        <v>29.13461765723405</v>
       </c>
     </row>
     <row r="219">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>28.11793192388021</v>
+        <v>32.64442480970493</v>
       </c>
     </row>
     <row r="220">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>30.64722848068376</v>
+        <v>15.98903773708224</v>
       </c>
     </row>
     <row r="221">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>24.44882088656185</v>
+        <v>30.30769145498891</v>
       </c>
     </row>
     <row r="222">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>34.39022301280647</v>
+        <v>30.46750795630783</v>
       </c>
     </row>
     <row r="223">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>20.89352381307214</v>
+        <v>24.75682008606106</v>
       </c>
     </row>
     <row r="224">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>28.89147416625847</v>
+        <v>28.98977593450654</v>
       </c>
     </row>
     <row r="225">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>27.85998067207154</v>
+        <v>32.33886061093406</v>
       </c>
     </row>
     <row r="226">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>30.37848658018573</v>
+        <v>15.79830296147626</v>
       </c>
     </row>
     <row r="227">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>24.40272842975289</v>
+        <v>30.48166748876465</v>
       </c>
     </row>
     <row r="228">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>33.91876454126455</v>
+        <v>30.01353828839505</v>
       </c>
     </row>
     <row r="229">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>21.00560378466258</v>
+        <v>25.35349209701874</v>
       </c>
     </row>
     <row r="230">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>29.67888606756471</v>
+        <v>28.60540465286982</v>
       </c>
     </row>
     <row r="231">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>27.8686775212863</v>
+        <v>31.98783579441977</v>
       </c>
     </row>
     <row r="232">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>31.01821393934398</v>
+        <v>15.96577866481706</v>
       </c>
     </row>
     <row r="233">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>24.17090728805646</v>
+        <v>30.54121131398233</v>
       </c>
     </row>
     <row r="234">
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>34.75082461988752</v>
+        <v>30.45000698383927</v>
       </c>
     </row>
     <row r="235">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>20.78205515058013</v>
+        <v>24.98991384848164</v>
       </c>
     </row>
     <row r="236">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>28.81783618800371</v>
+        <v>28.89256564630306</v>
       </c>
     </row>
     <row r="237">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>28.02452360944054</v>
+        <v>32.09046227818327</v>
       </c>
     </row>
     <row r="238">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>30.18200833780461</v>
+        <v>15.79495832299273</v>
       </c>
     </row>
     <row r="239">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>24.29766018545764</v>
+        <v>30.09613802764359</v>
       </c>
     </row>
     <row r="240">
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>34.22711999396716</v>
+        <v>30.55622356415909</v>
       </c>
     </row>
     <row r="241">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>20.77355492529803</v>
+        <v>24.79735129227493</v>
       </c>
     </row>
     <row r="242">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>27.69549436659453</v>
+        <v>29.02451536523277</v>
       </c>
     </row>
     <row r="243">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>27.00306059738566</v>
+        <v>22.36270474569161</v>
       </c>
     </row>
     <row r="244">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>21.92188395201839</v>
+        <v>25.24710414769315</v>
       </c>
     </row>
     <row r="245">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>30.22813228434276</v>
+        <v>28.83643555795685</v>
       </c>
     </row>
     <row r="246">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>27.96465457200469</v>
+        <v>34.15056137677244</v>
       </c>
     </row>
     <row r="247">
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>30.37230640707619</v>
+        <v>24.03717928657334</v>
       </c>
     </row>
     <row r="248">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>28.06161607141452</v>
+        <v>29.3377984289354</v>
       </c>
     </row>
     <row r="249">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>26.37254480673009</v>
+        <v>22.32107531592501</v>
       </c>
     </row>
     <row r="250">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>21.48630261199635</v>
+        <v>25.02484515905266</v>
       </c>
     </row>
     <row r="251">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>29.86634827071052</v>
+        <v>29.0672094852888</v>
       </c>
     </row>
     <row r="252">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>28.4065554848563</v>
+        <v>33.93505337503788</v>
       </c>
     </row>
     <row r="253">
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>30.02669172511998</v>
+        <v>23.64125398313965</v>
       </c>
     </row>
     <row r="254">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>27.89499109775855</v>
+        <v>29.0558456028002</v>
       </c>
     </row>
     <row r="255">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>26.66508131193297</v>
+        <v>22.38692058250046</v>
       </c>
     </row>
     <row r="256">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>21.52961271744196</v>
+        <v>25.22145199606594</v>
       </c>
     </row>
     <row r="257">
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>30.45856793143744</v>
+        <v>29.42776725204962</v>
       </c>
     </row>
     <row r="258">
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>28.25583366651533</v>
+        <v>34.72900592267152</v>
       </c>
     </row>
     <row r="259">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>30.38548742590624</v>
+        <v>23.94039489463883</v>
       </c>
     </row>
     <row r="260">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>27.97322438998012</v>
+        <v>29.26054094834307</v>
       </c>
     </row>
     <row r="261">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>26.31101169677933</v>
+        <v>22.20989151065052</v>
       </c>
     </row>
     <row r="262">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>21.54193872312522</v>
+        <v>25.13862482788148</v>
       </c>
     </row>
     <row r="263">
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>29.77109110884435</v>
+        <v>28.91620443972791</v>
       </c>
     </row>
     <row r="264">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>27.58048462053506</v>
+        <v>34.54480601747952</v>
       </c>
     </row>
     <row r="265">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>29.50334832291697</v>
+        <v>23.78038654071459</v>
       </c>
     </row>
     <row r="266">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>28.21035341336024</v>
+        <v>29.41809875462659</v>
       </c>
     </row>
     <row r="267">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>26.2691836476769</v>
+        <v>22.7786740566631</v>
       </c>
     </row>
     <row r="268">
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>21.957884528304</v>
+        <v>25.11593376917311</v>
       </c>
     </row>
     <row r="269">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>30.07761258331605</v>
+        <v>29.11641125899098</v>
       </c>
     </row>
     <row r="270">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>28.40702883873739</v>
+        <v>34.6713241225988</v>
       </c>
     </row>
     <row r="271">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>29.98784742154112</v>
+        <v>23.88253851028252</v>
       </c>
     </row>
     <row r="272">
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>27.7382138046033</v>
+        <v>29.33168939578223</v>
       </c>
     </row>
     <row r="273">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>26.58276819573032</v>
+        <v>22.43763211993449</v>
       </c>
     </row>
     <row r="274">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>21.79050724751803</v>
+        <v>25.16783861203077</v>
       </c>
     </row>
     <row r="275">
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>29.51179448529111</v>
+        <v>28.7757430184253</v>
       </c>
     </row>
     <row r="276">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>28.43776195577552</v>
+        <v>34.44212188971942</v>
       </c>
     </row>
     <row r="277">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>29.99406543957371</v>
+        <v>24.09815989481555</v>
       </c>
     </row>
     <row r="278">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>27.94551818216612</v>
+        <v>29.69079948207868</v>
       </c>
     </row>
     <row r="279">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>26.45242423397816</v>
+        <v>22.65001759793227</v>
       </c>
     </row>
     <row r="280">
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>21.3979433284949</v>
+        <v>25.68466032383</v>
       </c>
     </row>
     <row r="281">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>30.15306770913</v>
+        <v>28.7773850577043</v>
       </c>
     </row>
     <row r="282">
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>28.55853473700517</v>
+        <v>34.73405424946419</v>
       </c>
     </row>
     <row r="283">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>29.90596986850489</v>
+        <v>24.02270926287277</v>
       </c>
     </row>
     <row r="284">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>28.15362943816656</v>
+        <v>29.90697630509682</v>
       </c>
     </row>
     <row r="285">
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>26.12141325493272</v>
+        <v>22.25346687849758</v>
       </c>
     </row>
     <row r="286">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>21.35797047600099</v>
+        <v>24.93214602647758</v>
       </c>
     </row>
     <row r="287">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>29.55068908734235</v>
+        <v>28.82609184133769</v>
       </c>
     </row>
     <row r="288">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>28.41617696771539</v>
+        <v>33.70234663165332</v>
       </c>
     </row>
     <row r="289">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>29.48125222182376</v>
+        <v>23.85267668671973</v>
       </c>
     </row>
     <row r="290">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>33.17946765510813</v>
+        <v>26.45301894287697</v>
       </c>
     </row>
     <row r="291">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>27.76605875876434</v>
+        <v>26.63507762620971</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>24.57911195620843</v>
+        <v>29.67112573435474</v>
       </c>
     </row>
     <row r="293">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>31.20653628400258</v>
+        <v>29.46310115289606</v>
       </c>
     </row>
     <row r="294">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>28.06266205665846</v>
+        <v>28.68074163836922</v>
       </c>
     </row>
     <row r="295">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>27.97540545039952</v>
+        <v>27.84019991018853</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>33.84341717593075</v>
+        <v>26.41589280984012</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>28.00458364391239</v>
+        <v>26.72590657652815</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>24.0405647676623</v>
+        <v>29.1796743985436</v>
       </c>
     </row>
     <row r="299">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>31.32725856007287</v>
+        <v>29.45017019633031</v>
       </c>
     </row>
     <row r="300">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>27.80750720203176</v>
+        <v>28.74580681175474</v>
       </c>
     </row>
     <row r="301">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>27.73137065706267</v>
+        <v>27.8703656288721</v>
       </c>
     </row>
     <row r="302">
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>33.26428796948102</v>
+        <v>26.1987262290957</v>
       </c>
     </row>
     <row r="303">
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>27.98761119558209</v>
+        <v>26.95514372273376</v>
       </c>
     </row>
     <row r="304">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>24.41912809958805</v>
+        <v>29.5361987486131</v>
       </c>
     </row>
     <row r="305">
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>31.65357019373381</v>
+        <v>29.27848581201093</v>
       </c>
     </row>
     <row r="306">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>27.37002651439098</v>
+        <v>27.95773102070302</v>
       </c>
     </row>
     <row r="307">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>27.77643469122015</v>
+        <v>27.83390753567346</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>33.54085703642179</v>
+        <v>26.65676627909538</v>
       </c>
     </row>
     <row r="309">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>27.95731612173426</v>
+        <v>26.60757480459009</v>
       </c>
     </row>
     <row r="310">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>24.10529591085661</v>
+        <v>29.43698359191132</v>
       </c>
     </row>
     <row r="311">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>30.96136972589564</v>
+        <v>29.10063444108391</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>27.64457152816048</v>
+        <v>28.10740074437057</v>
       </c>
     </row>
     <row r="313">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>27.76613930184232</v>
+        <v>27.96187425167716</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>33.57046999349766</v>
+        <v>26.68743379559405</v>
       </c>
     </row>
     <row r="315">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>28.02512952648664</v>
+        <v>26.73189569886224</v>
       </c>
     </row>
     <row r="316">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>24.49865959276603</v>
+        <v>29.78049326423044</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>31.29919882773843</v>
+        <v>28.59525095593398</v>
       </c>
     </row>
     <row r="318">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>27.77775217200644</v>
+        <v>27.97486651654892</v>
       </c>
     </row>
     <row r="319">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>27.52315849148129</v>
+        <v>28.35951476904194</v>
       </c>
     </row>
     <row r="320">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>33.85956880295198</v>
+        <v>26.74394807625156</v>
       </c>
     </row>
     <row r="321">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>28.18544445620648</v>
+        <v>26.39601968269633</v>
       </c>
     </row>
     <row r="322">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>24.29111752728461</v>
+        <v>30.02874495700152</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>31.36816047942404</v>
+        <v>28.95395679325184</v>
       </c>
     </row>
     <row r="324">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>27.8826303934463</v>
+        <v>28.74576620242208</v>
       </c>
     </row>
     <row r="325">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>27.67242228038597</v>
+        <v>28.02064934077672</v>
       </c>
     </row>
     <row r="326">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>33.67384339814065</v>
+        <v>27.2046685059067</v>
       </c>
     </row>
     <row r="327">
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>28.32407032984672</v>
+        <v>27.06191458416295</v>
       </c>
     </row>
     <row r="328">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>24.7035309368722</v>
+        <v>29.4964493903923</v>
       </c>
     </row>
     <row r="329">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>31.45546168696109</v>
+        <v>29.20148631410503</v>
       </c>
     </row>
     <row r="330">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>28.04477515564096</v>
+        <v>28.59407533873767</v>
       </c>
     </row>
     <row r="331">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>27.84362807957203</v>
+        <v>28.38498368035059</v>
       </c>
     </row>
     <row r="332">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>33.01930089337686</v>
+        <v>26.39816464695118</v>
       </c>
     </row>
     <row r="333">
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>28.13592841460885</v>
+        <v>26.77753621449802</v>
       </c>
     </row>
     <row r="334">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>24.59069050413607</v>
+        <v>29.88304510226989</v>
       </c>
     </row>
     <row r="335">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>31.64144848742452</v>
+        <v>28.41186679923126</v>
       </c>
     </row>
     <row r="336">
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>27.35457641501443</v>
+        <v>28.07454713302252</v>
       </c>
     </row>
     <row r="337">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>27.37402386209934</v>
+        <v>27.43072243577382</v>
       </c>
     </row>
     <row r="338">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>31.51048184288915</v>
+        <v>29.2026384638177</v>
       </c>
     </row>
     <row r="339">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>27.11201325431221</v>
+        <v>30.93257902903899</v>
       </c>
     </row>
     <row r="340">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>29.69549013239058</v>
+        <v>23.61147112517853</v>
       </c>
     </row>
     <row r="341">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>24.04402035424124</v>
+        <v>27.10261274250927</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>29.21428010374946</v>
+        <v>29.29310240126282</v>
       </c>
     </row>
     <row r="343">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>29.38631578956175</v>
+        <v>20.01223748859628</v>
       </c>
     </row>
     <row r="344">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>31.64181026861563</v>
+        <v>28.78274854010469</v>
       </c>
     </row>
     <row r="345">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>27.01462784062903</v>
+        <v>30.69514604979343</v>
       </c>
     </row>
     <row r="346">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>29.33340855542288</v>
+        <v>23.35133421147205</v>
       </c>
     </row>
     <row r="347">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>24.09827052784859</v>
+        <v>27.0736914193375</v>
       </c>
     </row>
     <row r="348">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>29.53125238084446</v>
+        <v>28.22776273769819</v>
       </c>
     </row>
     <row r="349">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>29.49453204093082</v>
+        <v>20.27420720390161</v>
       </c>
     </row>
     <row r="350">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>31.86620729509612</v>
+        <v>28.89955633159597</v>
       </c>
     </row>
     <row r="351">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>26.64956369798982</v>
+        <v>30.9178771860367</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>29.50429902950926</v>
+        <v>23.34727099198109</v>
       </c>
     </row>
     <row r="353">
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>24.09123422841502</v>
+        <v>26.82800261414788</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>29.84414053962257</v>
+        <v>28.67556020763989</v>
       </c>
     </row>
     <row r="355">
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>29.43778376761604</v>
+        <v>20.07735300467299</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>31.80536666178724</v>
+        <v>29.2631714976385</v>
       </c>
     </row>
     <row r="357">
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>27.12675400997624</v>
+        <v>31.00555125030442</v>
       </c>
     </row>
     <row r="358">
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>29.51192484268571</v>
+        <v>23.03269341063235</v>
       </c>
     </row>
     <row r="359">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>23.66229489123959</v>
+        <v>27.21905461889997</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>29.70745054049908</v>
+        <v>28.67083580515452</v>
       </c>
     </row>
     <row r="361">
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>28.4987953424984</v>
+        <v>20.13139963433389</v>
       </c>
     </row>
     <row r="362">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>32.12619692026055</v>
+        <v>29.25018477161604</v>
       </c>
     </row>
     <row r="363">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>27.30234673850719</v>
+        <v>30.39426021910589</v>
       </c>
     </row>
     <row r="364">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>29.47539129484338</v>
+        <v>23.13320307159</v>
       </c>
     </row>
     <row r="365">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>24.12397146388378</v>
+        <v>26.75813015836751</v>
       </c>
     </row>
     <row r="366">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>29.89303665971735</v>
+        <v>29.38998153818003</v>
       </c>
     </row>
     <row r="367">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>29.11499370566098</v>
+        <v>20.29944748511542</v>
       </c>
     </row>
     <row r="368">
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>31.21309784439669</v>
+        <v>29.07663459430304</v>
       </c>
     </row>
     <row r="369">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>26.78916334413007</v>
+        <v>30.77792392441868</v>
       </c>
     </row>
     <row r="370">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>30.34604498568811</v>
+        <v>23.23586319089648</v>
       </c>
     </row>
     <row r="371">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>23.8930992592082</v>
+        <v>27.02270179610979</v>
       </c>
     </row>
     <row r="372">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>29.31521545390397</v>
+        <v>29.00070095750247</v>
       </c>
     </row>
     <row r="373">
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>29.55478419437644</v>
+        <v>20.44600737647483</v>
       </c>
     </row>
     <row r="374">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>31.65893374245231</v>
+        <v>29.12618606751351</v>
       </c>
     </row>
     <row r="375">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>27.1544621458586</v>
+        <v>30.53535948939236</v>
       </c>
     </row>
     <row r="376">
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>29.74516784298643</v>
+        <v>23.1980104275224</v>
       </c>
     </row>
     <row r="377">
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>23.71233985905886</v>
+        <v>26.4591271314441</v>
       </c>
     </row>
     <row r="378">
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>30.05600803974308</v>
+        <v>28.38694178501519</v>
       </c>
     </row>
     <row r="379">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>28.77036138814645</v>
+        <v>20.56966181583805</v>
       </c>
     </row>
     <row r="380">
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>31.72282794252184</v>
+        <v>29.76319652362181</v>
       </c>
     </row>
     <row r="381">
@@ -6527,7 +6527,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>27.0994628714455</v>
+        <v>30.63572151207531</v>
       </c>
     </row>
     <row r="382">
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>29.93694828499462</v>
+        <v>23.39611157388414</v>
       </c>
     </row>
     <row r="383">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>24.37849404272714</v>
+        <v>27.16684045577297</v>
       </c>
     </row>
     <row r="384">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>29.62048259901244</v>
+        <v>29.71112215511457</v>
       </c>
     </row>
     <row r="385">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>29.0144681155782</v>
+        <v>20.51947910913864</v>
       </c>
     </row>
   </sheetData>
